--- a/database/event/4327/event_4327_evp_summary.xlsx
+++ b/database/event/4327/event_4327_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7551</v>
+        <v>6.6718</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9633</v>
+        <v>2.276</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9036</v>
+        <v>2.2141</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7551</v>
+        <v>6.6718</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1898</v>
+        <v>4.1065</v>
       </c>
       <c r="G2" t="n">
         <v>2.5653</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1898</v>
+        <v>4.136</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1898</v>
+        <v>4.136</v>
       </c>
       <c r="J2" t="n">
         <v>2.5653</v>
@@ -529,7 +529,7 @@
         <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>5.755100000000001</v>
+        <v>6.7013</v>
       </c>
       <c r="N2" t="n">
         <v>171</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.647</v>
+        <v>4.3473</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2441</v>
+        <v>1.483</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0519</v>
+        <v>1.2881</v>
       </c>
       <c r="E3" t="n">
-        <v>3.647</v>
+        <v>4.3473</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7801</v>
+        <v>4.4804</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1331</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7801</v>
+        <v>4.7223</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8154</v>
+        <v>4.8021</v>
       </c>
       <c r="J3" t="n">
         <v>-0.1331</v>
@@ -575,7 +575,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6823</v>
+        <v>4.669</v>
       </c>
       <c r="N3" t="n">
         <v>185</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.6097</v>
+        <v>3.0165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8903</v>
+        <v>1.029</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6329</v>
+        <v>0.7579</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6097</v>
+        <v>3.0165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5323</v>
+        <v>0.9391</v>
       </c>
       <c r="G4" t="n">
         <v>2.0774</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5323</v>
+        <v>0.9391</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5323</v>
+        <v>0.9391</v>
       </c>
       <c r="J4" t="n">
         <v>2.0774</v>
@@ -621,7 +621,7 @@
         <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6097</v>
+        <v>3.0165</v>
       </c>
       <c r="N4" t="n">
         <v>171</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2028</v>
+        <v>2.7253</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.9297</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4685</v>
+        <v>0.6418</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2028</v>
+        <v>2.7253</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2028</v>
+        <v>2.0741</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.6512</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2028</v>
+        <v>2.0741</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2028</v>
+        <v>2.0741</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.6512</v>
       </c>
       <c r="K5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2028</v>
+        <v>2.7253</v>
       </c>
       <c r="N5" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.0752</v>
+        <v>2.5706</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7079</v>
+        <v>0.8769</v>
       </c>
       <c r="D6" t="n">
-        <v>0.417</v>
+        <v>0.5802</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0752</v>
+        <v>2.5706</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0752</v>
+        <v>2.5706</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0752</v>
+        <v>2.5706</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0752</v>
+        <v>2.5706</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0752</v>
+        <v>2.5706</v>
       </c>
       <c r="N6" t="n">
         <v>130</v>
@@ -722,32 +722,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.9378</v>
+        <v>2.4656</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6611</v>
+        <v>0.8411</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3615</v>
+        <v>0.5384</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9378</v>
+        <v>2.4656</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9378</v>
+        <v>2.4656</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9378</v>
+        <v>2.4656</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9378</v>
+        <v>2.4656</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9378</v>
+        <v>2.4656</v>
       </c>
       <c r="N7" t="n">
         <v>120</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8262</v>
+        <v>2.3874</v>
       </c>
       <c r="C8" t="n">
-        <v>0.623</v>
+        <v>0.8144</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3164</v>
+        <v>0.5072</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8262</v>
+        <v>2.3874</v>
       </c>
       <c r="F8" t="n">
-        <v>1.175</v>
+        <v>2.3874</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6512</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.175</v>
+        <v>2.3874</v>
       </c>
       <c r="I8" t="n">
-        <v>1.175</v>
+        <v>2.3874</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6512</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8262</v>
+        <v>2.3874</v>
       </c>
       <c r="N8" t="n">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5649</v>
+        <v>2.3381</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.7976</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2108</v>
+        <v>0.4876</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5649</v>
+        <v>2.3381</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5649</v>
+        <v>2.3381</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5649</v>
+        <v>2.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5649</v>
+        <v>2.3381</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5649</v>
+        <v>2.3381</v>
       </c>
       <c r="N9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4025</v>
+        <v>1.9451</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4784</v>
+        <v>0.6635</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1452</v>
+        <v>0.331</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4025</v>
+        <v>1.9451</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4025</v>
+        <v>1.9451</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4025</v>
+        <v>1.9451</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4025</v>
+        <v>1.9451</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4025</v>
+        <v>1.9451</v>
       </c>
       <c r="N10" t="n">
         <v>118</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3079</v>
+        <v>1.8875</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4462</v>
+        <v>0.6439</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107</v>
+        <v>0.3081</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3079</v>
+        <v>1.8875</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3079</v>
+        <v>1.8875</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3079</v>
+        <v>1.8875</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3079</v>
+        <v>1.8875</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3079</v>
+        <v>1.8875</v>
       </c>
       <c r="N11" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.159</v>
+        <v>1.6842</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3954</v>
+        <v>0.5745</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0468</v>
+        <v>0.2271</v>
       </c>
       <c r="E12" t="n">
-        <v>1.159</v>
+        <v>1.6842</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1567</v>
+        <v>2.6819</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9977</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1567</v>
+        <v>2.6819</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1769</v>
+        <v>2.7272</v>
       </c>
       <c r="J12" t="n">
         <v>-0.9977</v>
@@ -989,7 +989,7 @@
         <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1792</v>
+        <v>1.7295</v>
       </c>
       <c r="N12" t="n">
         <v>185</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0638</v>
+        <v>1.662</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3629</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.2182</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0638</v>
+        <v>1.662</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1429</v>
+        <v>1.662</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0791</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1429</v>
+        <v>1.662</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1429</v>
+        <v>1.662</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0791</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0638</v>
+        <v>1.662</v>
       </c>
       <c r="N13" t="n">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9287</v>
+        <v>1.6415</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0462</v>
+        <v>0.2101</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9287</v>
+        <v>1.6415</v>
       </c>
       <c r="F14" t="n">
-        <v>0.472</v>
+        <v>1.1848</v>
       </c>
       <c r="G14" t="n">
         <v>0.4567</v>
       </c>
       <c r="H14" t="n">
-        <v>0.472</v>
+        <v>1.1848</v>
       </c>
       <c r="I14" t="n">
-        <v>0.472</v>
+        <v>1.1848</v>
       </c>
       <c r="J14" t="n">
         <v>0.4567</v>
@@ -1081,7 +1081,7 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9287</v>
+        <v>1.6415</v>
       </c>
       <c r="N14" t="n">
         <v>171</v>
@@ -1090,231 +1090,231 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9212</v>
+        <v>1.403</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3143</v>
+        <v>0.4786</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0492</v>
+        <v>0.115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9212</v>
+        <v>1.403</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3827</v>
+        <v>1.4821</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4615</v>
+        <v>-0.0791</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3827</v>
+        <v>1.4821</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3956</v>
+        <v>1.4821</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4615</v>
+        <v>-0.0791</v>
       </c>
       <c r="K15" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L15" t="n">
         <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9340999999999999</v>
+        <v>1.403</v>
       </c>
       <c r="N15" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7352</v>
+        <v>1.2532</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2508</v>
+        <v>0.4275</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1244</v>
+        <v>0.0554</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7352</v>
+        <v>1.2532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7352</v>
+        <v>1.7147</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.4615</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7352</v>
+        <v>1.7147</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7352</v>
+        <v>1.7437</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.4615</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7352</v>
+        <v>1.2822</v>
       </c>
       <c r="N16" t="n">
-        <v>130</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7313</v>
+        <v>0.8008</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2495</v>
+        <v>0.2732</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1259</v>
+        <v>-0.1249</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7313</v>
+        <v>0.8008</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7313</v>
+        <v>0.8008</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7313</v>
+        <v>0.8008</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7313</v>
+        <v>0.8008</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7313</v>
+        <v>0.8008</v>
       </c>
       <c r="N17" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1414</v>
+        <v>0.5296</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0482</v>
+        <v>0.1807</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3642</v>
+        <v>-0.2329</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1414</v>
+        <v>0.5296</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1414</v>
+        <v>0.5296</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1414</v>
+        <v>0.5296</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1414</v>
+        <v>0.5296</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1414</v>
+        <v>0.5296</v>
       </c>
       <c r="N18" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.213</v>
+        <v>0.3838</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0727</v>
+        <v>0.1309</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5074</v>
+        <v>-0.291</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.213</v>
+        <v>0.3838</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.213</v>
+        <v>0.3838</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.213</v>
+        <v>0.3838</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.213</v>
+        <v>0.3838</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.213</v>
+        <v>0.3838</v>
       </c>
       <c r="N19" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3301</v>
+        <v>0.1762</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1126</v>
+        <v>0.0601</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5547</v>
+        <v>-0.3737</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3301</v>
+        <v>0.1762</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2196</v>
+        <v>0.7259</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5497</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2196</v>
+        <v>0.7259</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2216</v>
+        <v>0.7382</v>
       </c>
       <c r="J20" t="n">
         <v>-0.5497</v>
@@ -1357,7 +1357,7 @@
         <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3280999999999999</v>
+        <v>0.1885</v>
       </c>
       <c r="N20" t="n">
         <v>185</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4197</v>
+        <v>-0.0387</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1432</v>
+        <v>-0.0132</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5909</v>
+        <v>-0.4593</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4197</v>
+        <v>-0.0387</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4197</v>
+        <v>-0.0387</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4197</v>
+        <v>-0.0387</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4197</v>
+        <v>-0.0387</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4197</v>
+        <v>-0.0387</v>
       </c>
       <c r="N21" t="n">
         <v>118</v>
@@ -1412,32 +1412,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4689</v>
+        <v>-0.4669</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.16</v>
+        <v>-0.1593</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6108</v>
+        <v>-0.6299</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4689</v>
+        <v>-0.4669</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4689</v>
+        <v>-0.4669</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4689</v>
+        <v>-0.4669</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4689</v>
+        <v>-0.4669</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4689</v>
+        <v>-0.4669</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4806</v>
+        <v>-0.4689</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.164</v>
+        <v>-0.16</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6155</v>
+        <v>-0.6307</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4806</v>
+        <v>-0.4689</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4806</v>
+        <v>-0.4689</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4806</v>
+        <v>-0.4689</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4806</v>
+        <v>-0.4689</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4806</v>
+        <v>-0.4689</v>
       </c>
       <c r="N23" t="n">
         <v>118</v>
@@ -1514,7 +1514,7 @@
         <v>-0.1885</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6446</v>
+        <v>-0.6641</v>
       </c>
       <c r="E24" t="n">
         <v>-0.5526</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6893</v>
+        <v>-0.5914</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2351</v>
+        <v>-0.2017</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6998</v>
+        <v>-0.6795</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6893</v>
+        <v>-0.5914</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6893</v>
+        <v>-0.5914</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6893</v>
+        <v>-0.5914</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6893</v>
+        <v>-0.5914</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6893</v>
+        <v>-0.5914</v>
       </c>
       <c r="N25" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.8132</v>
+        <v>-0.6893</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2774</v>
+        <v>-0.2351</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7499</v>
+        <v>-0.7185</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8132</v>
+        <v>-0.6893</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8132</v>
+        <v>-0.6893</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8132</v>
+        <v>-0.6893</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8132</v>
+        <v>-0.6893</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8132</v>
+        <v>-0.6893</v>
       </c>
       <c r="N26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8152</v>
+        <v>-0.8164</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2781</v>
+        <v>-0.2785</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7507</v>
+        <v>-0.7692</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8152</v>
+        <v>-0.8164</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1584</v>
+        <v>0.1572</v>
       </c>
       <c r="G27" t="n">
         <v>-0.9736</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1584</v>
+        <v>0.1572</v>
       </c>
       <c r="I27" t="n">
         <v>0.1599</v>
@@ -1698,7 +1698,7 @@
         <v>-0.4939</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0062</v>
+        <v>-1.0207</v>
       </c>
       <c r="E28" t="n">
         <v>-1.4478</v>
@@ -1744,7 +1744,7 @@
         <v>-0.4991</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0123</v>
+        <v>-1.0267</v>
       </c>
       <c r="E29" t="n">
         <v>-1.4629</v>
@@ -1790,7 +1790,7 @@
         <v>-0.5685</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0946</v>
+        <v>-1.1078</v>
       </c>
       <c r="E30" t="n">
         <v>-1.6664</v>
@@ -1836,7 +1836,7 @@
         <v>-0.7018</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2524</v>
+        <v>-1.2635</v>
       </c>
       <c r="E31" t="n">
         <v>-2.0572</v>

--- a/database/event/4327/event_4327_evp_summary.xlsx
+++ b/database/event/4327/event_4327_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6718</v>
+        <v>5.8402</v>
       </c>
       <c r="C2" t="n">
-        <v>2.276</v>
+        <v>1.9923</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2141</v>
+        <v>1.9985</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6718</v>
+        <v>5.8402</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1065</v>
+        <v>3.4644</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5653</v>
+        <v>2.3758</v>
       </c>
       <c r="H2" t="n">
-        <v>4.136</v>
+        <v>4.2475</v>
       </c>
       <c r="I2" t="n">
-        <v>4.136</v>
+        <v>4.2475</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5653</v>
+        <v>2.3758</v>
       </c>
       <c r="K2" t="n">
         <v>121</v>
@@ -529,7 +529,7 @@
         <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7013</v>
+        <v>6.6233</v>
       </c>
       <c r="N2" t="n">
         <v>171</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3473</v>
+        <v>3.3491</v>
       </c>
       <c r="C3" t="n">
-        <v>1.483</v>
+        <v>1.1425</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2881</v>
+        <v>0.8739</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3473</v>
+        <v>3.3491</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4804</v>
+        <v>3.503</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1331</v>
+        <v>-0.1539</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7223</v>
+        <v>4.3321</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8021</v>
+        <v>4.6958</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1331</v>
+        <v>-0.1539</v>
       </c>
       <c r="K3" t="n">
         <v>135</v>
@@ -575,7 +575,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>4.669</v>
+        <v>4.5419</v>
       </c>
       <c r="N3" t="n">
         <v>185</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0165</v>
+        <v>3.2028</v>
       </c>
       <c r="C4" t="n">
-        <v>1.029</v>
+        <v>1.0926</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7579</v>
+        <v>0.8079</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0165</v>
+        <v>3.2028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9391</v>
+        <v>1.3301</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0774</v>
+        <v>1.8727</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9391</v>
+        <v>1.3301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9391</v>
+        <v>1.3301</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0774</v>
+        <v>1.8727</v>
       </c>
       <c r="K4" t="n">
         <v>121</v>
@@ -621,7 +621,7 @@
         <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0165</v>
+        <v>3.2028</v>
       </c>
       <c r="N4" t="n">
         <v>171</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7253</v>
+        <v>2.9986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9297</v>
+        <v>1.0229</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6418</v>
+        <v>0.7157</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7253</v>
+        <v>2.9986</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0741</v>
+        <v>2.4484</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6512</v>
+        <v>0.5502</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0741</v>
+        <v>2.4484</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0741</v>
+        <v>2.4484</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6512</v>
+        <v>0.5502</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7253</v>
+        <v>2.9986</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -676,78 +676,78 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5706</v>
+        <v>2.6378</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8769</v>
+        <v>0.8999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5802</v>
+        <v>0.5528</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5706</v>
+        <v>2.6378</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5706</v>
+        <v>2.6378</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5706</v>
+        <v>2.6378</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5706</v>
+        <v>2.6378</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5706</v>
+        <v>2.6378</v>
       </c>
       <c r="N6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4656</v>
+        <v>2.5388</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8411</v>
+        <v>0.8661</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5384</v>
+        <v>0.5081</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4656</v>
+        <v>2.5388</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4656</v>
+        <v>2.5388</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4656</v>
+        <v>2.5388</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4656</v>
+        <v>2.5388</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4656</v>
+        <v>2.5388</v>
       </c>
       <c r="N7" t="n">
         <v>120</v>
@@ -768,78 +768,78 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3874</v>
+        <v>2.4884</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8144</v>
+        <v>0.8489</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5072</v>
+        <v>0.4854</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3874</v>
+        <v>2.4884</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3874</v>
+        <v>2.4884</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3874</v>
+        <v>2.4884</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3874</v>
+        <v>2.4884</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3874</v>
+        <v>2.4884</v>
       </c>
       <c r="N8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3381</v>
+        <v>2.4113</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7976</v>
+        <v>0.8226</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4876</v>
+        <v>0.4506</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3381</v>
+        <v>2.4113</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3381</v>
+        <v>2.4113</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3381</v>
+        <v>2.4113</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3381</v>
+        <v>2.4113</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3381</v>
+        <v>2.4113</v>
       </c>
       <c r="N9" t="n">
         <v>120</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9451</v>
+        <v>2.2891</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6635</v>
+        <v>0.7809</v>
       </c>
       <c r="D10" t="n">
-        <v>0.331</v>
+        <v>0.3954</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9451</v>
+        <v>2.2891</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9451</v>
+        <v>2.2891</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9451</v>
+        <v>2.2891</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9451</v>
+        <v>2.2891</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9451</v>
+        <v>2.2891</v>
       </c>
       <c r="N10" t="n">
         <v>118</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8875</v>
+        <v>2.1657</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6439</v>
+        <v>0.7388</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3081</v>
+        <v>0.3397</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8875</v>
+        <v>2.1657</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8875</v>
+        <v>1.5463</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.6194</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8875</v>
+        <v>1.5463</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8875</v>
+        <v>1.5463</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.6194</v>
       </c>
       <c r="K11" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8875</v>
+        <v>2.1657</v>
       </c>
       <c r="N11" t="n">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6842</v>
+        <v>2.0295</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5745</v>
+        <v>0.6923</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2271</v>
+        <v>0.2782</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6842</v>
+        <v>2.0295</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6819</v>
+        <v>2.0295</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9977</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6819</v>
+        <v>2.0295</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7272</v>
+        <v>2.0295</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9977</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7295</v>
+        <v>2.0295</v>
       </c>
       <c r="N12" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.662</v>
+        <v>2.0244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6906</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2182</v>
+        <v>0.2759</v>
       </c>
       <c r="E13" t="n">
-        <v>1.662</v>
+        <v>2.0244</v>
       </c>
       <c r="F13" t="n">
-        <v>1.662</v>
+        <v>2.0244</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.662</v>
+        <v>2.0244</v>
       </c>
       <c r="I13" t="n">
-        <v>1.662</v>
+        <v>2.0244</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.662</v>
+        <v>2.0244</v>
       </c>
       <c r="N13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6415</v>
+        <v>1.8262</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.623</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2101</v>
+        <v>0.1864</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6415</v>
+        <v>1.8262</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1848</v>
+        <v>2.5259</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4567</v>
+        <v>-0.6997</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1848</v>
+        <v>2.5259</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1848</v>
+        <v>2.7379</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4567</v>
+        <v>-0.6997</v>
       </c>
       <c r="K14" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L14" t="n">
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6415</v>
+        <v>2.0382</v>
       </c>
       <c r="N14" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.403</v>
+        <v>1.706</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4786</v>
+        <v>0.582</v>
       </c>
       <c r="D15" t="n">
-        <v>0.115</v>
+        <v>0.1322</v>
       </c>
       <c r="E15" t="n">
-        <v>1.403</v>
+        <v>1.706</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4821</v>
+        <v>1.6454</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0791</v>
+        <v>0.0606</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4821</v>
+        <v>1.6454</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4821</v>
+        <v>1.6454</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0791</v>
+        <v>0.0606</v>
       </c>
       <c r="K15" t="n">
         <v>121</v>
@@ -1127,7 +1127,7 @@
         <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.403</v>
+        <v>1.706</v>
       </c>
       <c r="N15" t="n">
         <v>171</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2532</v>
+        <v>1.4283</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4275</v>
+        <v>0.4872</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0554</v>
+        <v>0.0068</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2532</v>
+        <v>1.4283</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7147</v>
+        <v>1.7937</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4615</v>
+        <v>-0.3654</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7147</v>
+        <v>1.7937</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7437</v>
+        <v>1.9443</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4615</v>
+        <v>-0.3654</v>
       </c>
       <c r="K16" t="n">
         <v>135</v>
@@ -1173,7 +1173,7 @@
         <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2822</v>
+        <v>1.5789</v>
       </c>
       <c r="N16" t="n">
         <v>185</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8008</v>
+        <v>1.283</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2732</v>
+        <v>0.4377</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1249</v>
+        <v>-0.0588</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8008</v>
+        <v>1.283</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8008</v>
+        <v>1.283</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8008</v>
+        <v>1.283</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8008</v>
+        <v>1.283</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8008</v>
+        <v>1.283</v>
       </c>
       <c r="N17" t="n">
         <v>130</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5296</v>
+        <v>0.8034</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1807</v>
+        <v>0.2741</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2329</v>
+        <v>-0.2753</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5296</v>
+        <v>0.8034</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5296</v>
+        <v>0.8034</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5296</v>
+        <v>0.8034</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5296</v>
+        <v>0.8034</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5296</v>
+        <v>0.8034</v>
       </c>
       <c r="N18" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3838</v>
+        <v>0.7749</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1309</v>
+        <v>0.2643</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.291</v>
+        <v>-0.2882</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3838</v>
+        <v>0.7749</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3838</v>
+        <v>0.7749</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3838</v>
+        <v>0.7749</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3838</v>
+        <v>0.7749</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3838</v>
+        <v>0.7749</v>
       </c>
       <c r="N19" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1762</v>
+        <v>0.3823</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0601</v>
+        <v>0.1304</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3737</v>
+        <v>-0.4654</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1762</v>
+        <v>0.3823</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7259</v>
+        <v>0.3823</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5497</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7259</v>
+        <v>0.3823</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7382</v>
+        <v>0.3823</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5497</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1885</v>
+        <v>0.3823</v>
       </c>
       <c r="N20" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0387</v>
+        <v>0.355</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0132</v>
+        <v>0.1211</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4593</v>
+        <v>-0.4777</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0387</v>
+        <v>0.355</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0387</v>
+        <v>0.7539</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3989</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0387</v>
+        <v>0.7539</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0387</v>
+        <v>0.8172</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3989</v>
       </c>
       <c r="K21" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0387</v>
+        <v>0.4183000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>118</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.4669</v>
+        <v>0.099</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1593</v>
+        <v>0.0338</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6299</v>
+        <v>-0.5933</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4669</v>
+        <v>0.099</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4669</v>
+        <v>0.099</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4669</v>
+        <v>0.099</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4669</v>
+        <v>0.099</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4669</v>
+        <v>0.099</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4689</v>
+        <v>-0.0235</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.16</v>
+        <v>-0.008</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6307</v>
+        <v>-0.6486</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4689</v>
+        <v>-0.0235</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4689</v>
+        <v>-0.0235</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4689</v>
+        <v>-0.0235</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4689</v>
+        <v>-0.0235</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4689</v>
+        <v>-0.0235</v>
       </c>
       <c r="N23" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5526</v>
+        <v>-0.0516</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1885</v>
+        <v>-0.0176</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6641</v>
+        <v>-0.6613</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5526</v>
+        <v>-0.0516</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5526</v>
+        <v>-0.0516</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5526</v>
+        <v>-0.0516</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5526</v>
+        <v>-0.0516</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5526</v>
+        <v>-0.0516</v>
       </c>
       <c r="N24" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5914</v>
+        <v>-0.1129</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2017</v>
+        <v>-0.0385</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6795</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5914</v>
+        <v>-0.1129</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5914</v>
+        <v>-0.1129</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5914</v>
+        <v>-0.1129</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5914</v>
+        <v>-0.1129</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5914</v>
+        <v>-0.1129</v>
       </c>
       <c r="N25" t="n">
         <v>130</v>
@@ -1596,124 +1596,124 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6893</v>
+        <v>-0.2903</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2351</v>
+        <v>-0.099</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7185</v>
+        <v>-0.7691</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6893</v>
+        <v>-0.2903</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6893</v>
+        <v>0.3615</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.6518</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6893</v>
+        <v>0.3615</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6893</v>
+        <v>0.3919</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.6518</v>
       </c>
       <c r="K26" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6893</v>
+        <v>-0.2599</v>
       </c>
       <c r="N26" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8164</v>
+        <v>-0.3113</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2785</v>
+        <v>-0.1062</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7692</v>
+        <v>-0.7786</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8164</v>
+        <v>-0.3113</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1572</v>
+        <v>-0.3113</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9736</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1572</v>
+        <v>-0.3113</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1599</v>
+        <v>-0.3113</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9736</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="L27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8137000000000001</v>
+        <v>-0.3113</v>
       </c>
       <c r="N27" t="n">
-        <v>185</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>vice</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.4478</v>
+        <v>-0.8207</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4939</v>
+        <v>-0.28</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0207</v>
+        <v>-1.0085</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.4478</v>
+        <v>-0.8207</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.4478</v>
+        <v>-0.8207</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.4478</v>
+        <v>-0.8207</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.4478</v>
+        <v>-0.8207</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.4478</v>
+        <v>-0.8207</v>
       </c>
       <c r="N28" t="n">
         <v>130</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vice</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4629</v>
+        <v>-0.9298</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4991</v>
+        <v>-0.3172</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0267</v>
+        <v>-1.0578</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4629</v>
+        <v>-0.9298</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4629</v>
+        <v>-0.9298</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4629</v>
+        <v>-0.9298</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.4629</v>
+        <v>-0.9298</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.4629</v>
+        <v>-0.9298</v>
       </c>
       <c r="N29" t="n">
         <v>130</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.6664</v>
+        <v>-1.0431</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5685</v>
+        <v>-0.3558</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1078</v>
+        <v>-1.1089</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.6664</v>
+        <v>-1.0431</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.6664</v>
+        <v>-1.0431</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.6664</v>
+        <v>-1.0431</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.6664</v>
+        <v>-1.0431</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.6664</v>
+        <v>-1.0431</v>
       </c>
       <c r="N30" t="n">
         <v>130</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.0572</v>
+        <v>-1.5167</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.7018</v>
+        <v>-0.5174</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2635</v>
+        <v>-1.3227</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.0572</v>
+        <v>-1.5167</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.0572</v>
+        <v>-1.5167</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.0572</v>
+        <v>-1.5167</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.0572</v>
+        <v>-1.5167</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.0572</v>
+        <v>-1.5167</v>
       </c>
       <c r="N31" t="n">
         <v>130</v>
@@ -1969,10 +1969,10 @@
         <v>0.93</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0479</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.0538</v>
+        <v>-1.4564</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2878</v>
+        <v>-0.2207</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.3316</v>
+        <v>-4.8554</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.79</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2878</v>
+        <v>-0.2207</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.3316</v>
+        <v>-4.8554</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4829</v>
+        <v>-0.3234</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.6238</v>
+        <v>-7.1148</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.596</v>
+        <v>-0.3985</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.112</v>
+        <v>-8.766999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5147</v>
+        <v>1.3375</v>
       </c>
       <c r="J7" t="n">
-        <v>33.3234</v>
+        <v>29.425</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4403</v>
+        <v>1.2892</v>
       </c>
       <c r="J8" t="n">
-        <v>31.6866</v>
+        <v>28.3624</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5992</v>
+        <v>0.6818</v>
       </c>
       <c r="J9" t="n">
-        <v>13.1824</v>
+        <v>14.9996</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.11</v>
       </c>
       <c r="I10" t="n">
-        <v>0.218</v>
+        <v>0.3044</v>
       </c>
       <c r="J10" t="n">
-        <v>4.796</v>
+        <v>6.6968</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5844</v>
+        <v>-0.5143</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.8568</v>
+        <v>-11.3146</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>0.93</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0668</v>
+        <v>-0.0755</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8704</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>0.92</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0852</v>
+        <v>-0.0877</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3856</v>
+        <v>-2.4556</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1737</v>
+        <v>-0.1447</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.8636</v>
+        <v>-4.0516</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3776</v>
+        <v>-0.2533</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.5728</v>
+        <v>-7.0924</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7099</v>
+        <v>-0.479</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.8772</v>
+        <v>-13.412</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8594</v>
+        <v>1.5683</v>
       </c>
       <c r="J17" t="n">
-        <v>52.0632</v>
+        <v>43.9124</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0506</v>
+        <v>1.0383</v>
       </c>
       <c r="J18" t="n">
-        <v>29.4168</v>
+        <v>29.0724</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5053</v>
+        <v>0.5749</v>
       </c>
       <c r="J19" t="n">
-        <v>14.1484</v>
+        <v>16.0972</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1425</v>
+        <v>-0.0624</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.99</v>
+        <v>-1.7472</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7891</v>
+        <v>-0.739</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.0948</v>
+        <v>-20.692</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2606</v>
+        <v>0.2722</v>
       </c>
       <c r="J22" t="n">
-        <v>7.5574</v>
+        <v>7.8938</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2263</v>
+        <v>0.2293</v>
       </c>
       <c r="J23" t="n">
-        <v>6.5627</v>
+        <v>6.6497</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.144</v>
+        <v>-0.1038</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.176</v>
+        <v>-3.0102</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3902</v>
+        <v>-0.2485</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.3158</v>
+        <v>-7.2065</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.516</v>
+        <v>-0.3355</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.964</v>
+        <v>-9.7295</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5949</v>
+        <v>1.387</v>
       </c>
       <c r="J27" t="n">
-        <v>46.2521</v>
+        <v>40.223</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.46</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1321</v>
+        <v>1.086</v>
       </c>
       <c r="J28" t="n">
-        <v>32.8309</v>
+        <v>31.494</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7812</v>
+        <v>0.7887</v>
       </c>
       <c r="J29" t="n">
-        <v>22.6548</v>
+        <v>22.8723</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3656</v>
+        <v>-0.2872</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.6024</v>
+        <v>-8.328799999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9804</v>
+        <v>-0.9526</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.4316</v>
+        <v>-27.6254</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4442</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>11.5492</v>
+        <v>13.5122</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4025</v>
+        <v>0.4663</v>
       </c>
       <c r="J33" t="n">
-        <v>10.465</v>
+        <v>12.1238</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3143</v>
+        <v>0.3562</v>
       </c>
       <c r="J34" t="n">
-        <v>8.171799999999999</v>
+        <v>9.261200000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4456</v>
+        <v>-0.2817</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.5856</v>
+        <v>-7.3242</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4592</v>
+        <v>-0.2915</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.9392</v>
+        <v>-7.579</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.45</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1626</v>
+        <v>1.0979</v>
       </c>
       <c r="J37" t="n">
-        <v>30.2276</v>
+        <v>28.5454</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8152</v>
+        <v>0.7964</v>
       </c>
       <c r="J38" t="n">
-        <v>21.1952</v>
+        <v>20.7064</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5149</v>
+        <v>0.5023</v>
       </c>
       <c r="J39" t="n">
-        <v>13.3874</v>
+        <v>13.0598</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2291</v>
+        <v>-0.1607</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.9566</v>
+        <v>-4.1782</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9155</v>
+        <v>-0.881</v>
       </c>
       <c r="J41" t="n">
-        <v>-23.803</v>
+        <v>-22.906</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>0.97</v>
       </c>
       <c r="I42" t="n">
-        <v>0.043</v>
+        <v>-0.0049</v>
       </c>
       <c r="J42" t="n">
-        <v>0.903</v>
+        <v>-0.1029</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.78</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2893</v>
+        <v>-0.2266</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.0753</v>
+        <v>-4.7586</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.74</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3596</v>
+        <v>-0.2649</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.5516</v>
+        <v>-5.5629</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4712</v>
+        <v>-0.3196</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.895200000000001</v>
+        <v>-6.7116</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.49</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7328</v>
+        <v>-0.4971</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.3888</v>
+        <v>-10.4391</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4807</v>
+        <v>1.3247</v>
       </c>
       <c r="J47" t="n">
-        <v>31.0947</v>
+        <v>27.8187</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.56</v>
       </c>
       <c r="I48" t="n">
-        <v>1.231</v>
+        <v>1.1716</v>
       </c>
       <c r="J48" t="n">
-        <v>25.851</v>
+        <v>24.6036</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.44</v>
       </c>
       <c r="I49" t="n">
-        <v>0.97</v>
+        <v>1.0257</v>
       </c>
       <c r="J49" t="n">
-        <v>20.37</v>
+        <v>21.5397</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.42</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9116</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>19.1436</v>
+        <v>20.9265</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>1.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0107</v>
+        <v>0.0992</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2247</v>
+        <v>2.0832</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.42</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6454</v>
+        <v>0.7902</v>
       </c>
       <c r="J52" t="n">
-        <v>19.362</v>
+        <v>23.706</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.2</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3572</v>
+        <v>0.4174</v>
       </c>
       <c r="J53" t="n">
-        <v>10.716</v>
+        <v>12.522</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.04</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0668</v>
+        <v>0.1055</v>
       </c>
       <c r="J54" t="n">
-        <v>2.004</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2966</v>
+        <v>-0.1753</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.898</v>
+        <v>-5.259</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.327</v>
+        <v>-0.1965</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.81</v>
+        <v>-5.895</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>1.147</v>
+        <v>1.0855</v>
       </c>
       <c r="J57" t="n">
-        <v>34.41</v>
+        <v>32.565</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.11</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3766</v>
+        <v>0.3561</v>
       </c>
       <c r="J58" t="n">
-        <v>11.298</v>
+        <v>10.683</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.167</v>
+        <v>-0.1108</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.01</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2422</v>
+        <v>-0.1828</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.266</v>
+        <v>-5.484</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5137</v>
+        <v>-0.4539</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.411</v>
+        <v>-13.617</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0332</v>
+        <v>1.0145</v>
       </c>
       <c r="J62" t="n">
-        <v>26.8632</v>
+        <v>26.377</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8345</v>
+        <v>0.8269</v>
       </c>
       <c r="J63" t="n">
-        <v>21.697</v>
+        <v>21.4994</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.22</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6155</v>
+        <v>0.6141</v>
       </c>
       <c r="J64" t="n">
-        <v>16.003</v>
+        <v>15.9666</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.3914</v>
+        <v>-2.4674</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4375</v>
+        <v>-0.3656</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.375</v>
+        <v>-9.505599999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4832</v>
+        <v>0.5631</v>
       </c>
       <c r="J67" t="n">
-        <v>12.5632</v>
+        <v>14.6406</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0461</v>
+        <v>0.0164</v>
       </c>
       <c r="J68" t="n">
-        <v>1.1986</v>
+        <v>0.4264</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.361</v>
+        <v>-0.2289</v>
       </c>
       <c r="J69" t="n">
-        <v>-9.385999999999999</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3908</v>
+        <v>-0.2487</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.1608</v>
+        <v>-6.4662</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.434</v>
+        <v>-0.2781</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.284</v>
+        <v>-7.2306</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.654</v>
+        <v>1.4318</v>
       </c>
       <c r="J72" t="n">
-        <v>36.388</v>
+        <v>31.4996</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0142</v>
+        <v>1.0333</v>
       </c>
       <c r="J73" t="n">
-        <v>22.3124</v>
+        <v>22.7326</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9236</v>
+        <v>0.97</v>
       </c>
       <c r="J74" t="n">
-        <v>20.3192</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2791</v>
+        <v>0.3738</v>
       </c>
       <c r="J75" t="n">
-        <v>6.1402</v>
+        <v>8.223599999999999</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1173</v>
+        <v>0.2061</v>
       </c>
       <c r="J76" t="n">
-        <v>2.5806</v>
+        <v>4.5342</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.04</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2058</v>
+        <v>0.1914</v>
       </c>
       <c r="J77" t="n">
-        <v>4.5276</v>
+        <v>4.2108</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0005</v>
+        <v>-0.032</v>
       </c>
       <c r="J78" t="n">
-        <v>0.011</v>
+        <v>-0.704</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.79</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.303</v>
+        <v>-0.2233</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.666</v>
+        <v>-4.9126</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6548</v>
+        <v>-0.4391</v>
       </c>
       <c r="J80" t="n">
-        <v>-14.4056</v>
+        <v>-9.6602</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6676</v>
+        <v>-0.4484</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.6872</v>
+        <v>-9.864800000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1557</v>
+        <v>0.1505</v>
       </c>
       <c r="J82" t="n">
-        <v>4.3596</v>
+        <v>4.214</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.03</v>
+        <v>0.0078</v>
       </c>
       <c r="J83" t="n">
-        <v>0.84</v>
+        <v>0.2184</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0568</v>
+        <v>-0.0465</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.5904</v>
+        <v>-1.302</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1323</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.7044</v>
+        <v>-2.3408</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3715</v>
+        <v>-0.2333</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.402</v>
+        <v>-6.5324</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.175</v>
+        <v>1.1125</v>
       </c>
       <c r="J87" t="n">
-        <v>32.9</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.43</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0719</v>
+        <v>1.0474</v>
       </c>
       <c r="J88" t="n">
-        <v>30.0132</v>
+        <v>29.3272</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4801</v>
+        <v>0.5344</v>
       </c>
       <c r="J89" t="n">
-        <v>13.4428</v>
+        <v>14.9632</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1867</v>
+        <v>-0.1071</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.2276</v>
+        <v>-2.9988</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2285</v>
+        <v>-0.1482</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.398</v>
+        <v>-4.1496</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>0.97</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0717</v>
+        <v>0.028</v>
       </c>
       <c r="J92" t="n">
-        <v>1.6491</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.79</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2407</v>
+        <v>-0.2041</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.5361</v>
+        <v>-4.6943</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.64</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.5021</v>
+        <v>-0.3477</v>
       </c>
       <c r="J94" t="n">
-        <v>-11.5483</v>
+        <v>-7.9971</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.59</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.3939</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.3193</v>
+        <v>-9.059699999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.37</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8689</v>
+        <v>-0.6002</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.9847</v>
+        <v>-13.8046</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.63</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3527</v>
+        <v>1.2491</v>
       </c>
       <c r="J97" t="n">
-        <v>31.1121</v>
+        <v>28.7293</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.62</v>
       </c>
       <c r="I98" t="n">
-        <v>1.3333</v>
+        <v>1.2375</v>
       </c>
       <c r="J98" t="n">
-        <v>30.6659</v>
+        <v>28.4625</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.53</v>
       </c>
       <c r="I99" t="n">
-        <v>1.152</v>
+        <v>1.1319</v>
       </c>
       <c r="J99" t="n">
-        <v>26.496</v>
+        <v>26.0337</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.34</v>
       </c>
       <c r="I100" t="n">
-        <v>0.712</v>
+        <v>0.8324</v>
       </c>
       <c r="J100" t="n">
-        <v>16.376</v>
+        <v>19.1452</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1.21</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4192</v>
+        <v>0.5308</v>
       </c>
       <c r="J101" t="n">
-        <v>9.6416</v>
+        <v>12.2084</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.71</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2665</v>
+        <v>-0.2326</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.797</v>
+        <v>-4.1868</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.67</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3274</v>
+        <v>-0.2773</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.8932</v>
+        <v>-4.9914</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.41</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7658</v>
+        <v>-0.5304</v>
       </c>
       <c r="J104" t="n">
-        <v>-13.7844</v>
+        <v>-9.5472</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.4</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7805</v>
+        <v>-0.5401</v>
       </c>
       <c r="J105" t="n">
-        <v>-14.049</v>
+        <v>-9.7218</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.33</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8786</v>
+        <v>-0.6092</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.8148</v>
+        <v>-10.9656</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>2.16</v>
       </c>
       <c r="I107" t="n">
-        <v>2.0593</v>
+        <v>1.8253</v>
       </c>
       <c r="J107" t="n">
-        <v>37.0674</v>
+        <v>32.8554</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1829</v>
+        <v>1.1698</v>
       </c>
       <c r="J108" t="n">
-        <v>21.2922</v>
+        <v>21.0564</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.46</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9319</v>
+        <v>1.0408</v>
       </c>
       <c r="J109" t="n">
-        <v>16.7742</v>
+        <v>18.7344</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.35</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7016</v>
+        <v>0.8371</v>
       </c>
       <c r="J110" t="n">
-        <v>12.6288</v>
+        <v>15.0678</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.24</v>
       </c>
       <c r="I111" t="n">
-        <v>0.463</v>
+        <v>0.5853</v>
       </c>
       <c r="J111" t="n">
-        <v>8.334</v>
+        <v>10.5354</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.5</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7672</v>
+        <v>0.9548</v>
       </c>
       <c r="J112" t="n">
-        <v>23.016</v>
+        <v>28.644</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1785</v>
+        <v>0.1859</v>
       </c>
       <c r="J113" t="n">
-        <v>5.355</v>
+        <v>5.577</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="J114" t="n">
-        <v>2.916</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4652</v>
+        <v>-0.2968</v>
       </c>
       <c r="J115" t="n">
-        <v>-13.956</v>
+        <v>-8.904</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6322</v>
+        <v>-0.419</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.966</v>
+        <v>-12.57</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7387</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>22.161</v>
+        <v>21.639</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5887</v>
+        <v>0.575</v>
       </c>
       <c r="J118" t="n">
-        <v>17.661</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.19</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5622</v>
+        <v>0.5501</v>
       </c>
       <c r="J119" t="n">
-        <v>16.866</v>
+        <v>16.503</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.12</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3446</v>
+        <v>0.3724</v>
       </c>
       <c r="J120" t="n">
-        <v>10.338</v>
+        <v>11.172</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5346</v>
+        <v>-0.4699</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.038</v>
+        <v>-14.097</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9449</v>
+        <v>1.1254</v>
       </c>
       <c r="J122" t="n">
-        <v>28.347</v>
+        <v>33.762</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3655</v>
+        <v>0.4235</v>
       </c>
       <c r="J123" t="n">
-        <v>10.965</v>
+        <v>12.705</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.91</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2259</v>
+        <v>-0.1287</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.777</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3662</v>
+        <v>-0.2247</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.986</v>
+        <v>-6.741</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.65</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.592</v>
+        <v>-0.3886</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.76</v>
+        <v>-11.658</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2853</v>
+        <v>0.3198</v>
       </c>
       <c r="J127" t="n">
-        <v>8.558999999999999</v>
+        <v>9.593999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2017</v>
+        <v>0.2208</v>
       </c>
       <c r="J128" t="n">
-        <v>6.051</v>
+        <v>6.624</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1648</v>
+        <v>0.179</v>
       </c>
       <c r="J129" t="n">
-        <v>4.944</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1632</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.896</v>
+        <v>-2.712</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2836</v>
+        <v>-0.1694</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.507999999999999</v>
+        <v>-5.082</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2013</v>
+        <v>1.1509</v>
       </c>
       <c r="J132" t="n">
-        <v>27.6299</v>
+        <v>26.4707</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.46</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0327</v>
+        <v>1.0542</v>
       </c>
       <c r="J133" t="n">
-        <v>23.7521</v>
+        <v>24.2466</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.44</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9873</v>
+        <v>1.0278</v>
       </c>
       <c r="J134" t="n">
-        <v>22.7079</v>
+        <v>23.6394</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6912</v>
+        <v>0.7988</v>
       </c>
       <c r="J135" t="n">
-        <v>15.8976</v>
+        <v>18.3724</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>1.29</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6227</v>
+        <v>0.7313</v>
       </c>
       <c r="J136" t="n">
-        <v>14.3221</v>
+        <v>16.8199</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3368</v>
+        <v>0.3681</v>
       </c>
       <c r="J137" t="n">
-        <v>7.7464</v>
+        <v>8.4663</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2843</v>
+        <v>-0.2298</v>
       </c>
       <c r="J138" t="n">
-        <v>-6.5389</v>
+        <v>-5.2854</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.73</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3498</v>
+        <v>-0.2692</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.045400000000001</v>
+        <v>-6.1916</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.46</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.7618</v>
+        <v>-0.5192</v>
       </c>
       <c r="J140" t="n">
-        <v>-17.5214</v>
+        <v>-11.9416</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8119</v>
+        <v>-0.5566</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.6737</v>
+        <v>-12.8018</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.42</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1026</v>
+        <v>1.0588</v>
       </c>
       <c r="J142" t="n">
-        <v>28.6676</v>
+        <v>27.5288</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.25</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7228</v>
+        <v>0.7018</v>
       </c>
       <c r="J143" t="n">
-        <v>18.7928</v>
+        <v>18.2468</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.05</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1264</v>
+        <v>0.1734</v>
       </c>
       <c r="J144" t="n">
-        <v>3.2864</v>
+        <v>4.5084</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.93</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3598</v>
+        <v>-0.2915</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.354799999999999</v>
+        <v>-7.579</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.92</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3899</v>
+        <v>-0.3219</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.1374</v>
+        <v>-8.369400000000001</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>0.664</v>
+        <v>0.8128</v>
       </c>
       <c r="J147" t="n">
-        <v>17.264</v>
+        <v>21.1328</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1227</v>
+        <v>0.1197</v>
       </c>
       <c r="J148" t="n">
-        <v>3.1902</v>
+        <v>3.1122</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0824</v>
+        <v>-0.0485</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.1424</v>
+        <v>-1.261</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2219</v>
+        <v>-0.1323</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.7694</v>
+        <v>-3.4398</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6553</v>
+        <v>-0.4365</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.0378</v>
+        <v>-11.349</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>0.98</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0327</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>0.7848000000000001</v>
+        <v>-0.2112</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0694</v>
+        <v>-0.0767</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.6656</v>
+        <v>-1.8408</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.124</v>
+        <v>-0.1123</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.976</v>
+        <v>-2.6952</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5285</v>
+        <v>-0.3493</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.684</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.4428</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.8592</v>
+        <v>-10.6272</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.53</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2508</v>
+        <v>1.1647</v>
       </c>
       <c r="J157" t="n">
-        <v>30.0192</v>
+        <v>27.9528</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.41</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0039</v>
+        <v>1.0063</v>
       </c>
       <c r="J158" t="n">
-        <v>24.0936</v>
+        <v>24.1512</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5265</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>12.636</v>
+        <v>14.3352</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.1</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2081</v>
+        <v>0.2874</v>
       </c>
       <c r="J160" t="n">
-        <v>4.9944</v>
+        <v>6.8976</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>1.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="J161" t="n">
-        <v>2.172</v>
+        <v>4.0464</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3538</v>
+        <v>1.2399</v>
       </c>
       <c r="J162" t="n">
-        <v>28.4298</v>
+        <v>26.0379</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.45</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0293</v>
+        <v>1.0452</v>
       </c>
       <c r="J163" t="n">
-        <v>21.6153</v>
+        <v>21.9492</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9623</v>
+        <v>1.002</v>
       </c>
       <c r="J164" t="n">
-        <v>20.2083</v>
+        <v>21.042</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.6919</v>
       </c>
       <c r="J165" t="n">
-        <v>12.3942</v>
+        <v>14.5299</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.14</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2753</v>
+        <v>0.3712</v>
       </c>
       <c r="J166" t="n">
-        <v>5.7813</v>
+        <v>7.7952</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.01</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1639</v>
+        <v>0.1381</v>
       </c>
       <c r="J167" t="n">
-        <v>3.4419</v>
+        <v>2.9001</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0701</v>
+        <v>0.0249</v>
       </c>
       <c r="J168" t="n">
-        <v>1.4721</v>
+        <v>0.5229</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.58</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.612</v>
+        <v>-0.4115</v>
       </c>
       <c r="J169" t="n">
-        <v>-12.852</v>
+        <v>-8.641500000000001</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6391</v>
+        <v>-0.4302</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.4211</v>
+        <v>-9.0342</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7431</v>
+        <v>-0.5049</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.6051</v>
+        <v>-10.6029</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4327/event_4327_evp_summary.xlsx
+++ b/database/event/4327/event_4327_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8402</v>
+        <v>5.5411</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9923</v>
+        <v>1.8903</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9985</v>
+        <v>1.8982</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8402</v>
+        <v>5.5411</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4644</v>
+        <v>3.1186</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3758</v>
+        <v>2.4225</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2475</v>
+        <v>4.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2475</v>
+        <v>4.1008</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3758</v>
+        <v>2.4225</v>
       </c>
       <c r="K2" t="n">
         <v>121</v>
@@ -529,7 +529,7 @@
         <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6233</v>
+        <v>6.523299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>171</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3491</v>
+        <v>3.3236</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1425</v>
+        <v>1.1338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8739</v>
+        <v>0.8888</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3491</v>
+        <v>3.3236</v>
       </c>
       <c r="F3" t="n">
-        <v>3.503</v>
+        <v>1.3069</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1539</v>
+        <v>2.0167</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3321</v>
+        <v>1.3069</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6958</v>
+        <v>1.3069</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1539</v>
+        <v>2.0167</v>
       </c>
       <c r="K3" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L3" t="n">
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5419</v>
+        <v>3.3236</v>
       </c>
       <c r="N3" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2028</v>
+        <v>2.9959</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0926</v>
+        <v>1.022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8079</v>
+        <v>0.7396</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2028</v>
+        <v>2.9959</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3301</v>
+        <v>3.1865</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8727</v>
+        <v>-0.1906</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3301</v>
+        <v>4.2494</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3301</v>
+        <v>4.4712</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8727</v>
+        <v>-0.1906</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L4" t="n">
         <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2028</v>
+        <v>4.2806</v>
       </c>
       <c r="N4" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9986</v>
+        <v>2.9755</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0229</v>
+        <v>1.0151</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7157</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9986</v>
+        <v>2.9755</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4484</v>
+        <v>2.2955</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5502</v>
+        <v>0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4484</v>
+        <v>2.2991</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4484</v>
+        <v>2.2991</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5502</v>
+        <v>0.68</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9986</v>
+        <v>2.9791</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6378</v>
+        <v>2.4037</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8999</v>
+        <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5528</v>
+        <v>0.47</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6378</v>
+        <v>2.4037</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6378</v>
+        <v>2.4037</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6378</v>
+        <v>2.5361</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6378</v>
+        <v>2.5361</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6378</v>
+        <v>2.5361</v>
       </c>
       <c r="N6" t="n">
         <v>120</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5388</v>
+        <v>2.3628</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8661</v>
+        <v>0.806</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5081</v>
+        <v>0.4514</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5388</v>
+        <v>2.3628</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5388</v>
+        <v>2.3628</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5388</v>
+        <v>2.4466</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5388</v>
+        <v>2.4466</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5388</v>
+        <v>2.4466</v>
       </c>
       <c r="N7" t="n">
         <v>120</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4884</v>
+        <v>2.3355</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8489</v>
+        <v>0.7967</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4854</v>
+        <v>0.439</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4884</v>
+        <v>2.3355</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4884</v>
+        <v>2.3355</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4884</v>
+        <v>2.3867</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4884</v>
+        <v>2.3867</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4884</v>
+        <v>2.3867</v>
       </c>
       <c r="N8" t="n">
         <v>130</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4113</v>
+        <v>2.3223</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8226</v>
+        <v>0.7922</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4506</v>
+        <v>0.433</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4113</v>
+        <v>2.3223</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4113</v>
+        <v>2.3223</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4113</v>
+        <v>2.3578</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4113</v>
+        <v>2.3578</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4113</v>
+        <v>2.3578</v>
       </c>
       <c r="N9" t="n">
         <v>120</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2891</v>
+        <v>2.1391</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7809</v>
+        <v>0.7297</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3954</v>
+        <v>0.3496</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2891</v>
+        <v>2.1391</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2891</v>
+        <v>2.1391</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2891</v>
+        <v>2.1391</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2891</v>
+        <v>2.1391</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2891</v>
+        <v>2.1391</v>
       </c>
       <c r="N10" t="n">
         <v>118</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1657</v>
+        <v>2.1375</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7388</v>
+        <v>0.7292</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3397</v>
+        <v>0.3488</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1657</v>
+        <v>2.1375</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5463</v>
+        <v>2.1375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6194</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5463</v>
+        <v>2.1375</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5463</v>
+        <v>2.1375</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6194</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1657</v>
+        <v>2.1375</v>
       </c>
       <c r="N11" t="n">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0295</v>
+        <v>2.0842</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6923</v>
+        <v>0.711</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2782</v>
+        <v>0.3246</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0295</v>
+        <v>2.0842</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0295</v>
+        <v>1.4692</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0295</v>
+        <v>1.4692</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0295</v>
+        <v>1.4692</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="K12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0295</v>
+        <v>2.0842</v>
       </c>
       <c r="N12" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0244</v>
+        <v>1.9208</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6906</v>
+        <v>0.6553</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2759</v>
+        <v>0.2502</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0244</v>
+        <v>1.9208</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0244</v>
+        <v>1.9208</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0244</v>
+        <v>1.9208</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0244</v>
+        <v>1.9208</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0244</v>
+        <v>1.9208</v>
       </c>
       <c r="N13" t="n">
         <v>130</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8262</v>
+        <v>1.6713</v>
       </c>
       <c r="C14" t="n">
-        <v>0.623</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1864</v>
+        <v>0.1366</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8262</v>
+        <v>1.6713</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5259</v>
+        <v>1.5868</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6997</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5259</v>
+        <v>1.5868</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7379</v>
+        <v>1.5868</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6997</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L14" t="n">
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0382</v>
+        <v>1.6713</v>
       </c>
       <c r="N14" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.706</v>
+        <v>1.6619</v>
       </c>
       <c r="C15" t="n">
-        <v>0.582</v>
+        <v>0.5669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1322</v>
+        <v>0.1323</v>
       </c>
       <c r="E15" t="n">
-        <v>1.706</v>
+        <v>1.6619</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6454</v>
+        <v>2.3905</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0606</v>
+        <v>-0.7286</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6454</v>
+        <v>2.5071</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6454</v>
+        <v>2.638</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0606</v>
+        <v>-0.7286</v>
       </c>
       <c r="K15" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L15" t="n">
         <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.706</v>
+        <v>1.9094</v>
       </c>
       <c r="N15" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4283</v>
+        <v>1.389</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4872</v>
+        <v>0.4738</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0068</v>
+        <v>0.0081</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4283</v>
+        <v>1.389</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7937</v>
+        <v>1.7926</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3654</v>
+        <v>-0.4036</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7937</v>
+        <v>1.7926</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9443</v>
+        <v>1.8862</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3654</v>
+        <v>-0.4036</v>
       </c>
       <c r="K16" t="n">
         <v>135</v>
@@ -1173,7 +1173,7 @@
         <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5789</v>
+        <v>1.4826</v>
       </c>
       <c r="N16" t="n">
         <v>185</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.283</v>
+        <v>1.1346</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4377</v>
+        <v>0.3871</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0588</v>
+        <v>-0.1077</v>
       </c>
       <c r="E17" t="n">
-        <v>1.283</v>
+        <v>1.1346</v>
       </c>
       <c r="F17" t="n">
-        <v>1.283</v>
+        <v>1.1346</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.283</v>
+        <v>1.1346</v>
       </c>
       <c r="I17" t="n">
-        <v>1.283</v>
+        <v>1.1346</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.283</v>
+        <v>1.1346</v>
       </c>
       <c r="N17" t="n">
         <v>130</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8034</v>
+        <v>0.7242</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2741</v>
+        <v>0.2471</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2753</v>
+        <v>-0.2945</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8034</v>
+        <v>0.7242</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8034</v>
+        <v>0.7242</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8034</v>
+        <v>0.7242</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8034</v>
+        <v>0.7242</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8034</v>
+        <v>0.7242</v>
       </c>
       <c r="N18" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7749</v>
+        <v>0.6701</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2643</v>
+        <v>0.2286</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2882</v>
+        <v>-0.3192</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7749</v>
+        <v>0.6701</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7749</v>
+        <v>0.6701</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7749</v>
+        <v>0.6701</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7749</v>
+        <v>0.6701</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7749</v>
+        <v>0.6701</v>
       </c>
       <c r="N19" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3823</v>
+        <v>0.3566</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1304</v>
+        <v>0.1216</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4654</v>
+        <v>-0.4619</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3823</v>
+        <v>0.3566</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3823</v>
+        <v>0.7904</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.4338</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3823</v>
+        <v>0.7904</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3823</v>
+        <v>0.8317</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.4338</v>
       </c>
       <c r="K20" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3823</v>
+        <v>0.3979</v>
       </c>
       <c r="N20" t="n">
-        <v>118</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.355</v>
+        <v>0.3197</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1211</v>
+        <v>0.1091</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4777</v>
+        <v>-0.4787</v>
       </c>
       <c r="E21" t="n">
-        <v>0.355</v>
+        <v>0.3197</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7539</v>
+        <v>0.3197</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3989</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7539</v>
+        <v>0.3197</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8172</v>
+        <v>0.3197</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3989</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4183000000000001</v>
+        <v>0.3197</v>
       </c>
       <c r="N21" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.099</v>
+        <v>0.0454</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0338</v>
+        <v>0.0155</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5933</v>
+        <v>-0.6035</v>
       </c>
       <c r="E22" t="n">
-        <v>0.099</v>
+        <v>0.0454</v>
       </c>
       <c r="F22" t="n">
-        <v>0.099</v>
+        <v>0.0454</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.099</v>
+        <v>0.0454</v>
       </c>
       <c r="I22" t="n">
-        <v>0.099</v>
+        <v>0.0454</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.099</v>
+        <v>0.0454</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0369</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.008</v>
+        <v>-0.0126</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6486</v>
+        <v>-0.641</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0369</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0369</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0369</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0369</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0369</v>
       </c>
       <c r="N23" t="n">
         <v>120</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0516</v>
+        <v>-0.1036</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0176</v>
+        <v>-0.0353</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6613</v>
+        <v>-0.6714</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0516</v>
+        <v>-0.1036</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0516</v>
+        <v>-0.1036</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0516</v>
+        <v>-0.1036</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0516</v>
+        <v>-0.1036</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0516</v>
+        <v>-0.1036</v>
       </c>
       <c r="N24" t="n">
         <v>118</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1129</v>
+        <v>-0.1807</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0385</v>
+        <v>-0.0616</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7065</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1129</v>
+        <v>-0.1807</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1129</v>
+        <v>-0.1807</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1129</v>
+        <v>-0.1807</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1129</v>
+        <v>-0.1807</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1129</v>
+        <v>-0.1807</v>
       </c>
       <c r="N25" t="n">
         <v>130</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2903</v>
+        <v>-0.2609</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.099</v>
+        <v>-0.089</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7691</v>
+        <v>-0.743</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2903</v>
+        <v>-0.2609</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3615</v>
+        <v>0.4239</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6518</v>
+        <v>-0.6848</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3615</v>
+        <v>0.4239</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3919</v>
+        <v>0.446</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6518</v>
+        <v>-0.6848</v>
       </c>
       <c r="K26" t="n">
         <v>135</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2599</v>
+        <v>-0.2388</v>
       </c>
       <c r="N26" t="n">
         <v>185</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3113</v>
+        <v>-0.386</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1062</v>
+        <v>-0.1317</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7786</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3113</v>
+        <v>-0.386</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3113</v>
+        <v>-0.386</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3113</v>
+        <v>-0.386</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3113</v>
+        <v>-0.386</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3113</v>
+        <v>-0.386</v>
       </c>
       <c r="N27" t="n">
         <v>130</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8207</v>
+        <v>-0.8508</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.28</v>
+        <v>-0.2902</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0085</v>
+        <v>-1.0115</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8207</v>
+        <v>-0.8508</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8207</v>
+        <v>-0.8508</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8207</v>
+        <v>-0.8508</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8207</v>
+        <v>-0.8508</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.8207</v>
+        <v>-0.8508</v>
       </c>
       <c r="N28" t="n">
         <v>130</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9298</v>
+        <v>-0.9439</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3172</v>
+        <v>-0.322</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0578</v>
+        <v>-1.0539</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9298</v>
+        <v>-0.9439</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9298</v>
+        <v>-0.9439</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9298</v>
+        <v>-0.9439</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9298</v>
+        <v>-0.9439</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9298</v>
+        <v>-0.9439</v>
       </c>
       <c r="N29" t="n">
         <v>130</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.0431</v>
+        <v>-1.1092</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3558</v>
+        <v>-0.3784</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1089</v>
+        <v>-1.1291</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0431</v>
+        <v>-1.1092</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.0431</v>
+        <v>-1.1092</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.0431</v>
+        <v>-1.1092</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.0431</v>
+        <v>-1.1092</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.0431</v>
+        <v>-1.1092</v>
       </c>
       <c r="N30" t="n">
         <v>130</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.5167</v>
+        <v>-1.4568</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5174</v>
+        <v>-0.497</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3227</v>
+        <v>-1.2874</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.5167</v>
+        <v>-1.4568</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.5167</v>
+        <v>-1.4568</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.5167</v>
+        <v>-1.4568</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.5167</v>
+        <v>-1.4568</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.5167</v>
+        <v>-1.4568</v>
       </c>
       <c r="N31" t="n">
         <v>130</v>
@@ -1969,10 +1969,10 @@
         <v>0.93</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.4564</v>
+        <v>-1.8788</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2207</v>
+        <v>-0.2404</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.8554</v>
+        <v>-5.2888</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.79</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2207</v>
+        <v>-0.2404</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8554</v>
+        <v>-5.2888</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3234</v>
+        <v>-0.3411</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.1148</v>
+        <v>-7.5042</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3985</v>
+        <v>-0.413</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.766999999999999</v>
+        <v>-9.086</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3375</v>
+        <v>1.4281</v>
       </c>
       <c r="J7" t="n">
-        <v>29.425</v>
+        <v>31.4182</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2892</v>
+        <v>1.3598</v>
       </c>
       <c r="J8" t="n">
-        <v>28.3624</v>
+        <v>29.9156</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6818</v>
+        <v>0.6582</v>
       </c>
       <c r="J9" t="n">
-        <v>14.9996</v>
+        <v>14.4804</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.11</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3044</v>
+        <v>0.3179</v>
       </c>
       <c r="J10" t="n">
-        <v>6.6968</v>
+        <v>6.9938</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5143</v>
+        <v>-0.476</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.3146</v>
+        <v>-10.472</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>0.93</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0755</v>
+        <v>-0.0927</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.114</v>
+        <v>-2.5956</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>0.92</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0877</v>
+        <v>-0.1052</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4556</v>
+        <v>-2.9456</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1447</v>
+        <v>-0.1632</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.0516</v>
+        <v>-4.5696</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2533</v>
+        <v>-0.2718</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.0924</v>
+        <v>-7.6104</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.479</v>
+        <v>-0.4882</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.412</v>
+        <v>-13.6696</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5683</v>
+        <v>1.6988</v>
       </c>
       <c r="J17" t="n">
-        <v>43.9124</v>
+        <v>47.5664</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0383</v>
+        <v>0.9944</v>
       </c>
       <c r="J18" t="n">
-        <v>29.0724</v>
+        <v>27.8432</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5749</v>
+        <v>0.5605</v>
       </c>
       <c r="J19" t="n">
-        <v>16.0972</v>
+        <v>15.694</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0624</v>
+        <v>-0.0432</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7472</v>
+        <v>-1.2096</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.739</v>
+        <v>-0.6798</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.692</v>
+        <v>-19.0344</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2722</v>
+        <v>0.2713</v>
       </c>
       <c r="J22" t="n">
-        <v>7.8938</v>
+        <v>7.8677</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2293</v>
+        <v>0.2302</v>
       </c>
       <c r="J23" t="n">
-        <v>6.6497</v>
+        <v>6.6758</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1038</v>
+        <v>-0.1176</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.0102</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2485</v>
+        <v>-0.2639</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.2065</v>
+        <v>-7.6531</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3355</v>
+        <v>-0.3488</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.7295</v>
+        <v>-10.1152</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.387</v>
+        <v>1.3664</v>
       </c>
       <c r="J27" t="n">
-        <v>40.223</v>
+        <v>39.6256</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.46</v>
       </c>
       <c r="I28" t="n">
-        <v>1.086</v>
+        <v>1.044</v>
       </c>
       <c r="J28" t="n">
-        <v>31.494</v>
+        <v>30.276</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7887</v>
+        <v>0.7497</v>
       </c>
       <c r="J29" t="n">
-        <v>22.8723</v>
+        <v>21.7413</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2872</v>
+        <v>-0.2709</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.328799999999999</v>
+        <v>-7.8561</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9526</v>
+        <v>-0.8687</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.6254</v>
+        <v>-25.1923</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5102</v>
       </c>
       <c r="J32" t="n">
-        <v>13.5122</v>
+        <v>13.2652</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4663</v>
+        <v>0.461</v>
       </c>
       <c r="J33" t="n">
-        <v>12.1238</v>
+        <v>11.986</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3562</v>
+        <v>0.3584</v>
       </c>
       <c r="J34" t="n">
-        <v>9.261200000000001</v>
+        <v>9.3184</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2817</v>
+        <v>-0.2939</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.3242</v>
+        <v>-7.6414</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2915</v>
+        <v>-0.3034</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.579</v>
+        <v>-7.8884</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.45</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0979</v>
+        <v>1.0525</v>
       </c>
       <c r="J37" t="n">
-        <v>28.5454</v>
+        <v>27.365</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7964</v>
+        <v>0.7507</v>
       </c>
       <c r="J38" t="n">
-        <v>20.7064</v>
+        <v>19.5182</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5023</v>
+        <v>0.4895</v>
       </c>
       <c r="J39" t="n">
-        <v>13.0598</v>
+        <v>12.727</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1607</v>
+        <v>-0.1566</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.1782</v>
+        <v>-4.0716</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.881</v>
+        <v>-0.8101</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.906</v>
+        <v>-21.0626</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>0.97</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0049</v>
+        <v>-0.0231</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.1029</v>
+        <v>-0.4851</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.78</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2266</v>
+        <v>-0.2472</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.7586</v>
+        <v>-5.1912</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.74</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2649</v>
+        <v>-0.2847</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.5629</v>
+        <v>-5.9787</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3196</v>
+        <v>-0.3382</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.7116</v>
+        <v>-7.1022</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.49</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4971</v>
+        <v>-0.5067</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.4391</v>
+        <v>-10.6407</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3247</v>
+        <v>1.3092</v>
       </c>
       <c r="J47" t="n">
-        <v>27.8187</v>
+        <v>27.4932</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.56</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1716</v>
+        <v>1.1454</v>
       </c>
       <c r="J48" t="n">
-        <v>24.6036</v>
+        <v>24.0534</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.44</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0257</v>
+        <v>0.981</v>
       </c>
       <c r="J49" t="n">
-        <v>21.5397</v>
+        <v>20.601</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.42</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9486</v>
       </c>
       <c r="J50" t="n">
-        <v>20.9265</v>
+        <v>19.9206</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>1.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0992</v>
+        <v>0.1323</v>
       </c>
       <c r="J51" t="n">
-        <v>2.0832</v>
+        <v>2.7783</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.42</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7902</v>
+        <v>0.7582</v>
       </c>
       <c r="J52" t="n">
-        <v>23.706</v>
+        <v>22.746</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.2</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4174</v>
+        <v>0.4182</v>
       </c>
       <c r="J53" t="n">
-        <v>12.522</v>
+        <v>12.546</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.04</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1055</v>
+        <v>0.1172</v>
       </c>
       <c r="J54" t="n">
-        <v>3.165</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1753</v>
+        <v>-0.1868</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.259</v>
+        <v>-5.604</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1965</v>
+        <v>-0.2081</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.895</v>
+        <v>-6.243</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0855</v>
+        <v>1.0352</v>
       </c>
       <c r="J57" t="n">
-        <v>32.565</v>
+        <v>31.056</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.11</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3561</v>
+        <v>0.3534</v>
       </c>
       <c r="J58" t="n">
-        <v>10.683</v>
+        <v>10.602</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1108</v>
+        <v>-0.1113</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.324</v>
+        <v>-3.339</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1828</v>
+        <v>-0.1815</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.484</v>
+        <v>-5.445</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4539</v>
+        <v>-0.4335</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.617</v>
+        <v>-13.005</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0145</v>
+        <v>0.9571</v>
       </c>
       <c r="J62" t="n">
-        <v>26.377</v>
+        <v>24.8846</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8269</v>
+        <v>0.7803</v>
       </c>
       <c r="J63" t="n">
-        <v>21.4994</v>
+        <v>20.2878</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.22</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6141</v>
+        <v>0.5923</v>
       </c>
       <c r="J64" t="n">
-        <v>15.9666</v>
+        <v>15.3998</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.4674</v>
+        <v>-2.2724</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3656</v>
+        <v>-0.3471</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.505599999999999</v>
+        <v>-9.0246</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5631</v>
+        <v>0.5421</v>
       </c>
       <c r="J67" t="n">
-        <v>14.6406</v>
+        <v>14.0946</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0164</v>
+        <v>0.0117</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4264</v>
+        <v>0.3042</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2289</v>
+        <v>-0.2445</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.9514</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2487</v>
+        <v>-0.2641</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.4662</v>
+        <v>-6.8666</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2781</v>
+        <v>-0.293</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.2306</v>
+        <v>-7.618</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4318</v>
+        <v>1.4202</v>
       </c>
       <c r="J72" t="n">
-        <v>31.4996</v>
+        <v>31.2444</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0333</v>
+        <v>0.9878</v>
       </c>
       <c r="J73" t="n">
-        <v>22.7326</v>
+        <v>21.7316</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.97</v>
+        <v>0.9195</v>
       </c>
       <c r="J74" t="n">
-        <v>21.34</v>
+        <v>20.229</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3738</v>
+        <v>0.3841</v>
       </c>
       <c r="J75" t="n">
-        <v>8.223599999999999</v>
+        <v>8.450200000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2061</v>
+        <v>0.2296</v>
       </c>
       <c r="J76" t="n">
-        <v>4.5342</v>
+        <v>5.0512</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.04</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1914</v>
+        <v>0.1796</v>
       </c>
       <c r="J77" t="n">
-        <v>4.2108</v>
+        <v>3.9512</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.032</v>
+        <v>-0.0484</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.704</v>
+        <v>-1.0648</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.79</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2233</v>
+        <v>-0.2424</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.9126</v>
+        <v>-5.3328</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4391</v>
+        <v>-0.451</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.6602</v>
+        <v>-9.922000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4484</v>
+        <v>-0.4598</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.864800000000001</v>
+        <v>-10.1156</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1505</v>
+        <v>0.1559</v>
       </c>
       <c r="J82" t="n">
-        <v>4.214</v>
+        <v>4.3652</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0078</v>
+        <v>0.0055</v>
       </c>
       <c r="J83" t="n">
-        <v>0.2184</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0465</v>
+        <v>-0.0556</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.302</v>
+        <v>-1.5568</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0956</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.3408</v>
+        <v>-2.6768</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2333</v>
+        <v>-0.248</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.5324</v>
+        <v>-6.944</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1125</v>
+        <v>1.0736</v>
       </c>
       <c r="J87" t="n">
-        <v>31.15</v>
+        <v>30.0608</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.43</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0474</v>
+        <v>0.9979</v>
       </c>
       <c r="J88" t="n">
-        <v>29.3272</v>
+        <v>27.9412</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5344</v>
+        <v>0.5224</v>
       </c>
       <c r="J89" t="n">
-        <v>14.9632</v>
+        <v>14.6272</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1071</v>
+        <v>-0.0959</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.9988</v>
+        <v>-2.6852</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1482</v>
+        <v>-0.1373</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.1496</v>
+        <v>-3.8444</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>0.97</v>
       </c>
       <c r="I92" t="n">
-        <v>0.028</v>
+        <v>-0.0072</v>
       </c>
       <c r="J92" t="n">
-        <v>0.644</v>
+        <v>-0.1656</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.79</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2041</v>
+        <v>-0.2276</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.6943</v>
+        <v>-5.2348</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.64</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3477</v>
+        <v>-0.367</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.9971</v>
+        <v>-8.441000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.59</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3939</v>
+        <v>-0.411</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.059699999999999</v>
+        <v>-9.452999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.37</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6002</v>
+        <v>-0.6038</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.8046</v>
+        <v>-13.8874</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.63</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2491</v>
+        <v>1.2296</v>
       </c>
       <c r="J97" t="n">
-        <v>28.7293</v>
+        <v>28.2808</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.62</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2375</v>
+        <v>1.2171</v>
       </c>
       <c r="J98" t="n">
-        <v>28.4625</v>
+        <v>27.9933</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.53</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1319</v>
+        <v>1.1033</v>
       </c>
       <c r="J99" t="n">
-        <v>26.0337</v>
+        <v>25.3759</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.34</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8324</v>
+        <v>0.797</v>
       </c>
       <c r="J100" t="n">
-        <v>19.1452</v>
+        <v>18.331</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1.21</v>
       </c>
       <c r="I101" t="n">
-        <v>0.5308</v>
+        <v>0.53</v>
       </c>
       <c r="J101" t="n">
-        <v>12.2084</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.71</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2326</v>
+        <v>-0.2651</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.1868</v>
+        <v>-4.7718</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.67</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2773</v>
+        <v>-0.3071</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.9914</v>
+        <v>-5.5278</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.41</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5304</v>
+        <v>-0.5438</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.5472</v>
+        <v>-9.788399999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.4</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5401</v>
+        <v>-0.5527</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.7218</v>
+        <v>-9.948600000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.33</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6092</v>
+        <v>-0.6159</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.9656</v>
+        <v>-11.0862</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>2.16</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8253</v>
+        <v>1.8393</v>
       </c>
       <c r="J107" t="n">
-        <v>32.8554</v>
+        <v>33.1074</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1698</v>
+        <v>1.1463</v>
       </c>
       <c r="J108" t="n">
-        <v>21.0564</v>
+        <v>20.6334</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.46</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0408</v>
+        <v>1.0014</v>
       </c>
       <c r="J109" t="n">
-        <v>18.7344</v>
+        <v>18.0252</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.35</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8371</v>
+        <v>0.8043</v>
       </c>
       <c r="J110" t="n">
-        <v>15.0678</v>
+        <v>14.4774</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.24</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5853</v>
+        <v>0.5821</v>
       </c>
       <c r="J111" t="n">
-        <v>10.5354</v>
+        <v>10.4778</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.5</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9548</v>
+        <v>0.9022</v>
       </c>
       <c r="J112" t="n">
-        <v>28.644</v>
+        <v>27.066</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1859</v>
+        <v>0.1932</v>
       </c>
       <c r="J113" t="n">
-        <v>5.577</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0936</v>
+        <v>0.1013</v>
       </c>
       <c r="J114" t="n">
-        <v>2.808</v>
+        <v>3.039</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2968</v>
+        <v>-0.3095</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.904</v>
+        <v>-9.285</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.419</v>
+        <v>-0.4276</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.57</v>
+        <v>-12.828</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.6853</v>
       </c>
       <c r="J117" t="n">
-        <v>21.639</v>
+        <v>20.559</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.575</v>
+        <v>0.5553</v>
       </c>
       <c r="J118" t="n">
-        <v>17.25</v>
+        <v>16.659</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.19</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5501</v>
+        <v>0.533</v>
       </c>
       <c r="J119" t="n">
-        <v>16.503</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.12</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3724</v>
+        <v>0.3711</v>
       </c>
       <c r="J120" t="n">
-        <v>11.172</v>
+        <v>11.133</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4699</v>
+        <v>-0.4447</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.097</v>
+        <v>-13.341</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1254</v>
+        <v>1.0976</v>
       </c>
       <c r="J122" t="n">
-        <v>33.762</v>
+        <v>32.928</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4235</v>
+        <v>0.4226</v>
       </c>
       <c r="J123" t="n">
-        <v>12.705</v>
+        <v>12.678</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.91</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1287</v>
+        <v>-0.1398</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.861</v>
+        <v>-4.194</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2247</v>
+        <v>-0.237</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.741</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.65</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3886</v>
+        <v>-0.3973</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.658</v>
+        <v>-11.919</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3198</v>
+        <v>0.3238</v>
       </c>
       <c r="J127" t="n">
-        <v>9.593999999999999</v>
+        <v>9.714</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2208</v>
+        <v>0.2291</v>
       </c>
       <c r="J128" t="n">
-        <v>6.624</v>
+        <v>6.873</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.179</v>
+        <v>0.1883</v>
       </c>
       <c r="J129" t="n">
-        <v>5.37</v>
+        <v>5.649</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1008</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.712</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1694</v>
+        <v>-0.1821</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.082</v>
+        <v>-5.463</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1509</v>
+        <v>1.1223</v>
       </c>
       <c r="J132" t="n">
-        <v>26.4707</v>
+        <v>25.8129</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.46</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0542</v>
+        <v>1.0138</v>
       </c>
       <c r="J133" t="n">
-        <v>24.2466</v>
+        <v>23.3174</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.44</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0278</v>
+        <v>0.9828</v>
       </c>
       <c r="J134" t="n">
-        <v>23.6394</v>
+        <v>22.6044</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7988</v>
+        <v>0.7655</v>
       </c>
       <c r="J135" t="n">
-        <v>18.3724</v>
+        <v>17.6065</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>1.29</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7313</v>
+        <v>0.7059</v>
       </c>
       <c r="J136" t="n">
-        <v>16.8199</v>
+        <v>16.2357</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3681</v>
+        <v>0.3374</v>
       </c>
       <c r="J137" t="n">
-        <v>8.4663</v>
+        <v>7.7602</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2298</v>
+        <v>-0.2517</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.2854</v>
+        <v>-5.7891</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.73</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2692</v>
+        <v>-0.2901</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.1916</v>
+        <v>-6.6723</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.46</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5192</v>
+        <v>-0.5282</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.9416</v>
+        <v>-12.1486</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5566</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.8018</v>
+        <v>-12.949</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.42</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0588</v>
+        <v>1.0061</v>
       </c>
       <c r="J142" t="n">
-        <v>27.5288</v>
+        <v>26.1586</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.25</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7018</v>
+        <v>0.6672</v>
       </c>
       <c r="J143" t="n">
-        <v>18.2468</v>
+        <v>17.3472</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.05</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1734</v>
+        <v>0.1841</v>
       </c>
       <c r="J144" t="n">
-        <v>4.5084</v>
+        <v>4.7866</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.93</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2915</v>
+        <v>-0.2814</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.579</v>
+        <v>-7.3164</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.92</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3219</v>
+        <v>-0.3098</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.369400000000001</v>
+        <v>-8.0548</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8128</v>
+        <v>0.7723</v>
       </c>
       <c r="J147" t="n">
-        <v>21.1328</v>
+        <v>20.0798</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1197</v>
+        <v>0.1272</v>
       </c>
       <c r="J148" t="n">
-        <v>3.1122</v>
+        <v>3.3072</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0485</v>
+        <v>-0.0571</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.261</v>
+        <v>-1.4846</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1323</v>
+        <v>-0.1454</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.4398</v>
+        <v>-3.7804</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4365</v>
+        <v>-0.4445</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.349</v>
+        <v>-11.557</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>0.98</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0217</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.2112</v>
+        <v>-0.5208</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0767</v>
+        <v>-0.0936</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.8408</v>
+        <v>-2.2464</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1123</v>
+        <v>-0.1301</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.6952</v>
+        <v>-3.1224</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3493</v>
+        <v>-0.3648</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.3832</v>
+        <v>-8.7552</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4428</v>
+        <v>-0.4539</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.6272</v>
+        <v>-10.8936</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.53</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1647</v>
+        <v>1.132</v>
       </c>
       <c r="J157" t="n">
-        <v>27.9528</v>
+        <v>27.168</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.41</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0063</v>
+        <v>0.9533</v>
       </c>
       <c r="J158" t="n">
-        <v>24.1512</v>
+        <v>22.8792</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5809</v>
       </c>
       <c r="J159" t="n">
-        <v>14.3352</v>
+        <v>13.9416</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.1</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2874</v>
+        <v>0.2998</v>
       </c>
       <c r="J160" t="n">
-        <v>6.8976</v>
+        <v>7.1952</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>1.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1686</v>
+        <v>0.1889</v>
       </c>
       <c r="J161" t="n">
-        <v>4.0464</v>
+        <v>4.5336</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2399</v>
+        <v>1.2169</v>
       </c>
       <c r="J162" t="n">
-        <v>26.0379</v>
+        <v>25.5549</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.45</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0452</v>
+        <v>1.0021</v>
       </c>
       <c r="J163" t="n">
-        <v>21.9492</v>
+        <v>21.0441</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>1.002</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>21.042</v>
+        <v>20.0151</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6919</v>
+        <v>0.6698</v>
       </c>
       <c r="J165" t="n">
-        <v>14.5299</v>
+        <v>14.0658</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.14</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3712</v>
+        <v>0.3822</v>
       </c>
       <c r="J166" t="n">
-        <v>7.7952</v>
+        <v>8.026199999999999</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.01</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1381</v>
+        <v>0.1167</v>
       </c>
       <c r="J167" t="n">
-        <v>2.9001</v>
+        <v>2.4507</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0249</v>
+        <v>-0.0041</v>
       </c>
       <c r="J168" t="n">
-        <v>0.5229</v>
+        <v>-0.0861</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.58</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4115</v>
+        <v>-0.4264</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.641500000000001</v>
+        <v>-8.9544</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4302</v>
+        <v>-0.444</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.0342</v>
+        <v>-9.324</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5049</v>
+        <v>-0.5142</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.6029</v>
+        <v>-10.7982</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4327/event_4327_evp_summary.xlsx
+++ b/database/event/4327/event_4327_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5411</v>
+        <v>5.5035</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8903</v>
+        <v>1.8775</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8982</v>
+        <v>1.9013</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5411</v>
+        <v>5.5035</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1186</v>
+        <v>3.0529</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4225</v>
+        <v>2.4506</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1008</v>
+        <v>4.0463</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1008</v>
+        <v>4.0463</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4225</v>
+        <v>2.4506</v>
       </c>
       <c r="K2" t="n">
         <v>121</v>
@@ -529,7 +529,7 @@
         <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>6.523299999999999</v>
+        <v>6.4969</v>
       </c>
       <c r="N2" t="n">
         <v>171</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3236</v>
+        <v>3.3052</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1338</v>
+        <v>1.1275</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8888</v>
+        <v>0.8999</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3236</v>
+        <v>3.3052</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3069</v>
+        <v>1.2847</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0167</v>
+        <v>2.0205</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3069</v>
+        <v>1.2847</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3069</v>
+        <v>1.2847</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0167</v>
+        <v>2.0205</v>
       </c>
       <c r="K3" t="n">
         <v>121</v>
@@ -575,7 +575,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3236</v>
+        <v>3.3052</v>
       </c>
       <c r="N3" t="n">
         <v>171</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.9959</v>
+        <v>3.0439</v>
       </c>
       <c r="C4" t="n">
-        <v>1.022</v>
+        <v>1.0384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7396</v>
+        <v>0.7809</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9959</v>
+        <v>3.0439</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1865</v>
+        <v>2.3015</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1906</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2494</v>
+        <v>2.3241</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4712</v>
+        <v>2.3241</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1906</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L4" t="n">
         <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2806</v>
+        <v>3.0665</v>
       </c>
       <c r="N4" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9755</v>
+        <v>2.951</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0151</v>
+        <v>1.0067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9755</v>
+        <v>2.951</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2955</v>
+        <v>3.1137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.68</v>
+        <v>-0.1627</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2991</v>
+        <v>4.1856</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2991</v>
+        <v>4.4123</v>
       </c>
       <c r="J5" t="n">
-        <v>0.68</v>
+        <v>-0.1627</v>
       </c>
       <c r="K5" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L5" t="n">
         <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9791</v>
+        <v>4.2496</v>
       </c>
       <c r="N5" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4037</v>
+        <v>2.3383</v>
       </c>
       <c r="C6" t="n">
-        <v>0.82</v>
+        <v>0.7977</v>
       </c>
       <c r="D6" t="n">
-        <v>0.47</v>
+        <v>0.4594</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4037</v>
+        <v>2.3383</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4037</v>
+        <v>2.3383</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5361</v>
+        <v>2.4086</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5361</v>
+        <v>2.4086</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5361</v>
+        <v>2.4086</v>
       </c>
       <c r="N6" t="n">
         <v>120</v>
@@ -722,32 +722,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3628</v>
+        <v>2.3324</v>
       </c>
       <c r="C7" t="n">
-        <v>0.806</v>
+        <v>0.7957</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4514</v>
+        <v>0.4567</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3628</v>
+        <v>2.3324</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3628</v>
+        <v>2.3324</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4466</v>
+        <v>2.395</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4466</v>
+        <v>2.395</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4466</v>
+        <v>2.395</v>
       </c>
       <c r="N7" t="n">
         <v>120</v>
@@ -768,231 +768,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3355</v>
+        <v>2.3219</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7967</v>
+        <v>0.7921</v>
       </c>
       <c r="D8" t="n">
-        <v>0.439</v>
+        <v>0.4519</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3355</v>
+        <v>2.3219</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3355</v>
+        <v>2.3219</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3867</v>
+        <v>2.3709</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3867</v>
+        <v>2.3709</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3867</v>
+        <v>2.3709</v>
       </c>
       <c r="N8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3223</v>
+        <v>2.2901</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7922</v>
+        <v>0.7812</v>
       </c>
       <c r="D9" t="n">
-        <v>0.433</v>
+        <v>0.4375</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3223</v>
+        <v>2.2901</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3223</v>
+        <v>2.2901</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3578</v>
+        <v>2.2981</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3578</v>
+        <v>2.2981</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3578</v>
+        <v>2.2981</v>
       </c>
       <c r="N9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1391</v>
+        <v>2.1404</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7297</v>
+        <v>0.7302</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3496</v>
+        <v>0.3693</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1391</v>
+        <v>2.1404</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1391</v>
+        <v>2.1404</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1391</v>
+        <v>2.1404</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1391</v>
+        <v>2.1404</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1391</v>
+        <v>2.1404</v>
       </c>
       <c r="N10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1375</v>
+        <v>2.1251</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7292</v>
+        <v>0.725</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3488</v>
+        <v>0.3623</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1375</v>
+        <v>2.1251</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1375</v>
+        <v>1.5305</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.5946</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1375</v>
+        <v>1.5305</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1375</v>
+        <v>1.5305</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.5946</v>
       </c>
       <c r="K11" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1375</v>
+        <v>2.1251</v>
       </c>
       <c r="N11" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0842</v>
+        <v>2.0802</v>
       </c>
       <c r="C12" t="n">
-        <v>0.711</v>
+        <v>0.7096</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3246</v>
+        <v>0.3418</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0842</v>
+        <v>2.0802</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4692</v>
+        <v>2.0802</v>
       </c>
       <c r="G12" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4692</v>
+        <v>2.0802</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4692</v>
+        <v>2.0802</v>
       </c>
       <c r="J12" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0842</v>
+        <v>2.0802</v>
       </c>
       <c r="N12" t="n">
-        <v>171</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9208</v>
+        <v>1.8473</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6553</v>
+        <v>0.6302</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2502</v>
+        <v>0.2357</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9208</v>
+        <v>1.8473</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9208</v>
+        <v>1.8473</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9208</v>
+        <v>1.8473</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9208</v>
+        <v>1.8473</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9208</v>
+        <v>1.8473</v>
       </c>
       <c r="N13" t="n">
         <v>130</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6713</v>
+        <v>1.6645</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5678</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1366</v>
+        <v>0.1525</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6713</v>
+        <v>1.6645</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5868</v>
+        <v>1.574</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0905</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5868</v>
+        <v>1.574</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5868</v>
+        <v>1.574</v>
       </c>
       <c r="J14" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0905</v>
       </c>
       <c r="K14" t="n">
         <v>121</v>
@@ -1081,7 +1081,7 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6713</v>
+        <v>1.6645</v>
       </c>
       <c r="N14" t="n">
         <v>171</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6619</v>
+        <v>1.6569</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5669</v>
+        <v>0.5652</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1323</v>
+        <v>0.149</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6619</v>
+        <v>1.6569</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3905</v>
+        <v>2.3672</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7286</v>
+        <v>-0.7103</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5071</v>
+        <v>2.4749</v>
       </c>
       <c r="I15" t="n">
-        <v>2.638</v>
+        <v>2.6089</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7286</v>
+        <v>-0.7103</v>
       </c>
       <c r="K15" t="n">
         <v>135</v>
@@ -1127,7 +1127,7 @@
         <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9094</v>
+        <v>1.8986</v>
       </c>
       <c r="N15" t="n">
         <v>185</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.389</v>
+        <v>1.4115</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4738</v>
+        <v>0.4815</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0081</v>
+        <v>0.0372</v>
       </c>
       <c r="E16" t="n">
-        <v>1.389</v>
+        <v>1.4115</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7926</v>
+        <v>1.783</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4036</v>
+        <v>-0.3715</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7926</v>
+        <v>1.783</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8862</v>
+        <v>1.8796</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4036</v>
+        <v>-0.3715</v>
       </c>
       <c r="K16" t="n">
         <v>135</v>
@@ -1173,7 +1173,7 @@
         <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4826</v>
+        <v>1.5081</v>
       </c>
       <c r="N16" t="n">
         <v>185</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1346</v>
+        <v>1.0732</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3871</v>
+        <v>0.3661</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1077</v>
+        <v>-0.1169</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1346</v>
+        <v>1.0732</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1346</v>
+        <v>1.0732</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1346</v>
+        <v>1.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1346</v>
+        <v>1.0732</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1346</v>
+        <v>1.0732</v>
       </c>
       <c r="N17" t="n">
         <v>130</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7242</v>
+        <v>0.7731</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2471</v>
+        <v>0.2637</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2945</v>
+        <v>-0.2536</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7242</v>
+        <v>0.7731</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7242</v>
+        <v>0.7731</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7242</v>
+        <v>0.7731</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7242</v>
+        <v>0.7731</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7242</v>
+        <v>0.7731</v>
       </c>
       <c r="N18" t="n">
         <v>130</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6701</v>
+        <v>0.6747</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2286</v>
+        <v>0.2302</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3192</v>
+        <v>-0.2984</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6701</v>
+        <v>0.6747</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6701</v>
+        <v>0.6747</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6701</v>
+        <v>0.6747</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6701</v>
+        <v>0.6747</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6701</v>
+        <v>0.6747</v>
       </c>
       <c r="N19" t="n">
         <v>118</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3566</v>
+        <v>0.4568</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1216</v>
+        <v>0.1558</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4619</v>
+        <v>-0.3977</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3566</v>
+        <v>0.4568</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7904</v>
+        <v>0.8623</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4338</v>
+        <v>-0.4055</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7904</v>
+        <v>0.8623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8317</v>
+        <v>0.909</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4338</v>
+        <v>-0.4055</v>
       </c>
       <c r="K20" t="n">
         <v>135</v>
@@ -1357,7 +1357,7 @@
         <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3979</v>
+        <v>0.5035000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>185</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3197</v>
+        <v>0.3382</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1091</v>
+        <v>0.1154</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4787</v>
+        <v>-0.4517</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3197</v>
+        <v>0.3382</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3197</v>
+        <v>0.3382</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3197</v>
+        <v>0.3382</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3197</v>
+        <v>0.3382</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3197</v>
+        <v>0.3382</v>
       </c>
       <c r="N21" t="n">
         <v>118</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0454</v>
+        <v>0.023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0155</v>
+        <v>0.0078</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6035</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0454</v>
+        <v>0.023</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0454</v>
+        <v>0.023</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0454</v>
+        <v>0.023</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0454</v>
+        <v>0.023</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0454</v>
+        <v>0.023</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0369</v>
+        <v>-0.051</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.641</v>
+        <v>-0.629</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0369</v>
+        <v>-0.051</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0369</v>
+        <v>-0.051</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0369</v>
+        <v>-0.051</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0369</v>
+        <v>-0.051</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0369</v>
+        <v>-0.051</v>
       </c>
       <c r="N23" t="n">
         <v>120</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1036</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0353</v>
+        <v>-0.0288</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6714</v>
+        <v>-0.6443</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1036</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1036</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1036</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1036</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1036</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>118</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1807</v>
+        <v>-0.1275</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0616</v>
+        <v>-0.0435</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7065</v>
+        <v>-0.6639</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1807</v>
+        <v>-0.1275</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1807</v>
+        <v>-0.1275</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1807</v>
+        <v>-0.1275</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1807</v>
+        <v>-0.1275</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1807</v>
+        <v>-0.1275</v>
       </c>
       <c r="N25" t="n">
         <v>130</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2609</v>
+        <v>-0.2793</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.089</v>
+        <v>-0.0953</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.743</v>
+        <v>-0.733</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2609</v>
+        <v>-0.2793</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4239</v>
+        <v>0.3776</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6848</v>
+        <v>-0.6569</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4239</v>
+        <v>0.3776</v>
       </c>
       <c r="I26" t="n">
-        <v>0.446</v>
+        <v>0.398</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6848</v>
+        <v>-0.6569</v>
       </c>
       <c r="K26" t="n">
         <v>135</v>
@@ -1633,7 +1633,7 @@
         <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2388</v>
+        <v>-0.2589</v>
       </c>
       <c r="N26" t="n">
         <v>185</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.386</v>
+        <v>-0.3657</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1317</v>
+        <v>-0.1248</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.7724</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.386</v>
+        <v>-0.3657</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.386</v>
+        <v>-0.3657</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.386</v>
+        <v>-0.3657</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.386</v>
+        <v>-0.3657</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.386</v>
+        <v>-0.3657</v>
       </c>
       <c r="N27" t="n">
         <v>130</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8508</v>
+        <v>-0.9205</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2902</v>
+        <v>-0.314</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.0115</v>
+        <v>-1.0251</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8508</v>
+        <v>-0.9205</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8508</v>
+        <v>-0.9205</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8508</v>
+        <v>-0.9205</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8508</v>
+        <v>-0.9205</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.8508</v>
+        <v>-0.9205</v>
       </c>
       <c r="N28" t="n">
         <v>130</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9439</v>
+        <v>-0.9926</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.322</v>
+        <v>-0.3386</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0539</v>
+        <v>-1.058</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9439</v>
+        <v>-0.9926</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9439</v>
+        <v>-0.9926</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9439</v>
+        <v>-0.9926</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9439</v>
+        <v>-0.9926</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9439</v>
+        <v>-0.9926</v>
       </c>
       <c r="N29" t="n">
         <v>130</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.1092</v>
+        <v>-1.0889</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3784</v>
+        <v>-0.3715</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1291</v>
+        <v>-1.1018</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.1092</v>
+        <v>-1.0889</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.1092</v>
+        <v>-1.0889</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.1092</v>
+        <v>-1.0889</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.1092</v>
+        <v>-1.0889</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.1092</v>
+        <v>-1.0889</v>
       </c>
       <c r="N30" t="n">
         <v>130</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.4568</v>
+        <v>-1.4423</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.497</v>
+        <v>-0.492</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.2874</v>
+        <v>-1.2628</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.4568</v>
+        <v>-1.4423</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.4568</v>
+        <v>-1.4423</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.4568</v>
+        <v>-1.4423</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.4568</v>
+        <v>-1.4423</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.4568</v>
+        <v>-1.4423</v>
       </c>
       <c r="N31" t="n">
         <v>130</v>
@@ -1969,10 +1969,10 @@
         <v>0.93</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0854</v>
+        <v>-0.0716</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.8788</v>
+        <v>-1.5752</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2404</v>
+        <v>-0.2244</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.2888</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.79</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2404</v>
+        <v>-0.2244</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.2888</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3411</v>
+        <v>-0.3263</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.5042</v>
+        <v>-7.1786</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.413</v>
+        <v>-0.4026</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.086</v>
+        <v>-8.857200000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4281</v>
+        <v>1.4635</v>
       </c>
       <c r="J7" t="n">
-        <v>31.4182</v>
+        <v>32.197</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3598</v>
+        <v>1.3934</v>
       </c>
       <c r="J8" t="n">
-        <v>29.9156</v>
+        <v>30.6548</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6582</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>14.4804</v>
+        <v>13.9172</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1.11</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3179</v>
+        <v>0.2861</v>
       </c>
       <c r="J10" t="n">
-        <v>6.9938</v>
+        <v>6.2942</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.476</v>
+        <v>-0.439</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.472</v>
+        <v>-9.657999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>0.93</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0927</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5956</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>0.92</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1052</v>
+        <v>-0.0911</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9456</v>
+        <v>-2.5508</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1632</v>
+        <v>-0.1471</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.5696</v>
+        <v>-4.1188</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2718</v>
+        <v>-0.2543</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.6104</v>
+        <v>-7.1204</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.52</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4882</v>
+        <v>-0.4859</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.6696</v>
+        <v>-13.6052</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6988</v>
+        <v>1.7344</v>
       </c>
       <c r="J17" t="n">
-        <v>47.5664</v>
+        <v>48.5632</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.43</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9944</v>
+        <v>0.9871</v>
       </c>
       <c r="J18" t="n">
-        <v>27.8432</v>
+        <v>27.6388</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5605</v>
+        <v>0.5295</v>
       </c>
       <c r="J19" t="n">
-        <v>15.694</v>
+        <v>14.826</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0432</v>
+        <v>-0.038</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2096</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6798</v>
+        <v>-0.651</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.0344</v>
+        <v>-18.228</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2713</v>
+        <v>0.2232</v>
       </c>
       <c r="J22" t="n">
-        <v>7.8677</v>
+        <v>6.4728</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2302</v>
+        <v>0.1856</v>
       </c>
       <c r="J23" t="n">
-        <v>6.6758</v>
+        <v>5.3824</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.92</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1176</v>
+        <v>-0.1011</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.4104</v>
+        <v>-2.9319</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2639</v>
+        <v>-0.2445</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.6531</v>
+        <v>-7.0905</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3488</v>
+        <v>-0.3336</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.1152</v>
+        <v>-9.6744</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3664</v>
+        <v>1.3908</v>
       </c>
       <c r="J27" t="n">
-        <v>39.6256</v>
+        <v>40.3332</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.46</v>
       </c>
       <c r="I28" t="n">
-        <v>1.044</v>
+        <v>1.0486</v>
       </c>
       <c r="J28" t="n">
-        <v>30.276</v>
+        <v>30.4094</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7497</v>
+        <v>0.7231</v>
       </c>
       <c r="J29" t="n">
-        <v>21.7413</v>
+        <v>20.9699</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2709</v>
+        <v>-0.233</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.8561</v>
+        <v>-6.757</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8687</v>
+        <v>-0.8558</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.1923</v>
+        <v>-24.8182</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5102</v>
+        <v>0.4508</v>
       </c>
       <c r="J32" t="n">
-        <v>13.2652</v>
+        <v>11.7208</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.461</v>
+        <v>0.4026</v>
       </c>
       <c r="J33" t="n">
-        <v>11.986</v>
+        <v>10.4676</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3584</v>
+        <v>0.3043</v>
       </c>
       <c r="J34" t="n">
-        <v>9.3184</v>
+        <v>7.9118</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2939</v>
+        <v>-0.2758</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.6414</v>
+        <v>-7.1708</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3034</v>
+        <v>-0.2859</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.8884</v>
+        <v>-7.4334</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.45</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0525</v>
+        <v>1.0587</v>
       </c>
       <c r="J37" t="n">
-        <v>27.365</v>
+        <v>27.5262</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.29</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7507</v>
+        <v>0.7209</v>
       </c>
       <c r="J38" t="n">
-        <v>19.5182</v>
+        <v>18.7434</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4895</v>
+        <v>0.4505</v>
       </c>
       <c r="J39" t="n">
-        <v>12.727</v>
+        <v>11.713</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1566</v>
+        <v>-0.1252</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.0716</v>
+        <v>-3.2552</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8101</v>
+        <v>-0.7885</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.0626</v>
+        <v>-20.501</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>0.97</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0231</v>
+        <v>-0.0119</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4851</v>
+        <v>-0.2499</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>0.78</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2472</v>
+        <v>-0.2319</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.1912</v>
+        <v>-4.8699</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.74</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2847</v>
+        <v>-0.2695</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.9787</v>
+        <v>-5.6595</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3382</v>
+        <v>-0.3238</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.1022</v>
+        <v>-6.7998</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.49</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5067</v>
+        <v>-0.506</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.6407</v>
+        <v>-10.626</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3092</v>
+        <v>1.3298</v>
       </c>
       <c r="J47" t="n">
-        <v>27.4932</v>
+        <v>27.9258</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.56</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1454</v>
+        <v>1.1614</v>
       </c>
       <c r="J48" t="n">
-        <v>24.0534</v>
+        <v>24.3894</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.44</v>
       </c>
       <c r="I49" t="n">
-        <v>0.981</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>20.601</v>
+        <v>20.6514</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.42</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9486</v>
+        <v>0.9468</v>
       </c>
       <c r="J50" t="n">
-        <v>19.9206</v>
+        <v>19.8828</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>1.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1323</v>
+        <v>0.1041</v>
       </c>
       <c r="J51" t="n">
-        <v>2.7783</v>
+        <v>2.1861</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.42</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7582</v>
+        <v>0.7019</v>
       </c>
       <c r="J52" t="n">
-        <v>22.746</v>
+        <v>21.057</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.2</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4182</v>
+        <v>0.3618</v>
       </c>
       <c r="J53" t="n">
-        <v>12.546</v>
+        <v>10.854</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.04</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1172</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>3.516</v>
+        <v>2.709</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1868</v>
+        <v>-0.1662</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.604</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2081</v>
+        <v>-0.1876</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.243</v>
+        <v>-5.628</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0352</v>
+        <v>1.0397</v>
       </c>
       <c r="J57" t="n">
-        <v>31.056</v>
+        <v>31.191</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>1.11</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3534</v>
+        <v>0.3138</v>
       </c>
       <c r="J58" t="n">
-        <v>10.602</v>
+        <v>9.414</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.98</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1113</v>
+        <v>-0.0852</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.339</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1815</v>
+        <v>-0.1475</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.445</v>
+        <v>-4.425</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4335</v>
+        <v>-0.3906</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.005</v>
+        <v>-11.718</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9571</v>
+        <v>0.9465</v>
       </c>
       <c r="J62" t="n">
-        <v>24.8846</v>
+        <v>24.609</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7803</v>
+        <v>0.7536</v>
       </c>
       <c r="J63" t="n">
-        <v>20.2878</v>
+        <v>19.5936</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.22</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5923</v>
+        <v>0.5573</v>
       </c>
       <c r="J64" t="n">
-        <v>15.3998</v>
+        <v>14.4898</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.2724</v>
+        <v>-1.7264</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.91</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3471</v>
+        <v>-0.3057</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.0246</v>
+        <v>-7.9482</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5421</v>
+        <v>0.4856</v>
       </c>
       <c r="J67" t="n">
-        <v>14.0946</v>
+        <v>12.6256</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0117</v>
+        <v>0.0077</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3042</v>
+        <v>0.2002</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2445</v>
+        <v>-0.2247</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.357</v>
+        <v>-5.8422</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.8666</v>
+        <v>-6.3622</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.293</v>
+        <v>-0.2746</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.618</v>
+        <v>-7.1396</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4202</v>
+        <v>1.4463</v>
       </c>
       <c r="J72" t="n">
-        <v>31.2444</v>
+        <v>31.8186</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9878</v>
+        <v>0.988</v>
       </c>
       <c r="J73" t="n">
-        <v>21.7316</v>
+        <v>21.736</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9195</v>
+        <v>0.9111</v>
       </c>
       <c r="J74" t="n">
-        <v>20.229</v>
+        <v>20.0442</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3841</v>
+        <v>0.3523</v>
       </c>
       <c r="J75" t="n">
-        <v>8.450200000000001</v>
+        <v>7.7506</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>1.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2296</v>
+        <v>0.199</v>
       </c>
       <c r="J76" t="n">
-        <v>5.0512</v>
+        <v>4.378</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.04</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1796</v>
+        <v>0.1472</v>
       </c>
       <c r="J77" t="n">
-        <v>3.9512</v>
+        <v>3.2384</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0484</v>
+        <v>-0.0374</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.0648</v>
+        <v>-0.8228</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.79</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2424</v>
+        <v>-0.2256</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.3328</v>
+        <v>-4.9632</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.451</v>
+        <v>-0.4442</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.922000000000001</v>
+        <v>-9.772399999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4598</v>
+        <v>-0.4539</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.1156</v>
+        <v>-9.985799999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1559</v>
+        <v>0.12</v>
       </c>
       <c r="J82" t="n">
-        <v>4.3652</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0055</v>
+        <v>0.0031</v>
       </c>
       <c r="J83" t="n">
-        <v>0.154</v>
+        <v>0.0868</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0556</v>
+        <v>-0.0443</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.5568</v>
+        <v>-1.2404</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0956</v>
+        <v>-0.0799</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.6768</v>
+        <v>-2.2372</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.248</v>
+        <v>-0.228</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.944</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.48</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0736</v>
+        <v>1.0823</v>
       </c>
       <c r="J87" t="n">
-        <v>30.0608</v>
+        <v>30.3044</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.43</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9979</v>
+        <v>0.9947</v>
       </c>
       <c r="J88" t="n">
-        <v>27.9412</v>
+        <v>27.8516</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5224</v>
+        <v>0.4887</v>
       </c>
       <c r="J89" t="n">
-        <v>14.6272</v>
+        <v>13.6836</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0959</v>
+        <v>-0.075</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.6852</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1373</v>
+        <v>-0.1103</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.8444</v>
+        <v>-3.0884</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>0.97</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0072</v>
+        <v>0.0128</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.1656</v>
+        <v>0.2944</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.79</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2276</v>
+        <v>-0.213</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.2348</v>
+        <v>-4.899</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.64</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.367</v>
+        <v>-0.3553</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.441000000000001</v>
+        <v>-8.171900000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.59</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.411</v>
+        <v>-0.4013</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.452999999999999</v>
+        <v>-9.229900000000001</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.37</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6038</v>
+        <v>-0.6168</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.8874</v>
+        <v>-14.1864</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.63</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2296</v>
+        <v>1.2482</v>
       </c>
       <c r="J97" t="n">
-        <v>28.2808</v>
+        <v>28.7086</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.62</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2171</v>
+        <v>1.2354</v>
       </c>
       <c r="J98" t="n">
-        <v>27.9933</v>
+        <v>28.4142</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.53</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1033</v>
+        <v>1.1199</v>
       </c>
       <c r="J99" t="n">
-        <v>25.3759</v>
+        <v>25.7577</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.34</v>
       </c>
       <c r="I100" t="n">
-        <v>0.797</v>
+        <v>0.7844</v>
       </c>
       <c r="J100" t="n">
-        <v>18.331</v>
+        <v>18.0412</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>1.21</v>
       </c>
       <c r="I101" t="n">
-        <v>0.53</v>
+        <v>0.5022</v>
       </c>
       <c r="J101" t="n">
-        <v>12.19</v>
+        <v>11.5506</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.71</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2651</v>
+        <v>-0.2488</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.7718</v>
+        <v>-4.4784</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.67</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3071</v>
+        <v>-0.2954</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.5278</v>
+        <v>-5.3172</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.41</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5438</v>
+        <v>-0.5473</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.788399999999999</v>
+        <v>-9.8514</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.4</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5527</v>
+        <v>-0.5571</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.948600000000001</v>
+        <v>-10.0278</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.33</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6159</v>
+        <v>-0.6286</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.0862</v>
+        <v>-11.3148</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>2.16</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8393</v>
+        <v>1.9005</v>
       </c>
       <c r="J107" t="n">
-        <v>33.1074</v>
+        <v>34.209</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.57</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1463</v>
+        <v>1.1664</v>
       </c>
       <c r="J108" t="n">
-        <v>20.6334</v>
+        <v>20.9952</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.46</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0014</v>
+        <v>1.0117</v>
       </c>
       <c r="J109" t="n">
-        <v>18.0252</v>
+        <v>18.2106</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.35</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8043</v>
+        <v>0.7943</v>
       </c>
       <c r="J110" t="n">
-        <v>14.4774</v>
+        <v>14.2974</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1.24</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5821</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>10.4778</v>
+        <v>10.026</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.5</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9022</v>
+        <v>0.8587</v>
       </c>
       <c r="J112" t="n">
-        <v>27.066</v>
+        <v>25.761</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1932</v>
+        <v>0.1529</v>
       </c>
       <c r="J113" t="n">
-        <v>5.796</v>
+        <v>4.587</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1013</v>
+        <v>0.0747</v>
       </c>
       <c r="J114" t="n">
-        <v>3.039</v>
+        <v>2.241</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3095</v>
+        <v>-0.2921</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.285</v>
+        <v>-8.763</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4276</v>
+        <v>-0.4202</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.828</v>
+        <v>-12.606</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6853</v>
+        <v>0.6521</v>
       </c>
       <c r="J117" t="n">
-        <v>20.559</v>
+        <v>19.563</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5553</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>16.659</v>
+        <v>15.528</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.19</v>
       </c>
       <c r="I119" t="n">
-        <v>0.533</v>
+        <v>0.4949</v>
       </c>
       <c r="J119" t="n">
-        <v>15.99</v>
+        <v>14.847</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.12</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3711</v>
+        <v>0.334</v>
       </c>
       <c r="J120" t="n">
-        <v>11.133</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4447</v>
+        <v>-0.4026</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.341</v>
+        <v>-12.078</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0976</v>
+        <v>1.0851</v>
       </c>
       <c r="J122" t="n">
-        <v>32.928</v>
+        <v>32.553</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4226</v>
+        <v>0.3657</v>
       </c>
       <c r="J123" t="n">
-        <v>12.678</v>
+        <v>10.971</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>0.91</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1398</v>
+        <v>-0.1203</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.194</v>
+        <v>-3.609</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>0.82</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.237</v>
+        <v>-0.2169</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.11</v>
+        <v>-6.507</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.65</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3973</v>
+        <v>-0.3874</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.919</v>
+        <v>-11.622</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3238</v>
+        <v>0.2718</v>
       </c>
       <c r="J127" t="n">
-        <v>9.714</v>
+        <v>8.154</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2291</v>
+        <v>0.1853</v>
       </c>
       <c r="J128" t="n">
-        <v>6.873</v>
+        <v>5.559</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>1.07</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1883</v>
+        <v>0.1493</v>
       </c>
       <c r="J129" t="n">
-        <v>5.649</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1008</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.024</v>
+        <v>-2.508</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1821</v>
+        <v>-0.1616</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.463</v>
+        <v>-4.848</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1223</v>
+        <v>1.1375</v>
       </c>
       <c r="J132" t="n">
-        <v>25.8129</v>
+        <v>26.1625</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.46</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0138</v>
+        <v>1.0196</v>
       </c>
       <c r="J133" t="n">
-        <v>23.3174</v>
+        <v>23.4508</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.44</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9828</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>22.6044</v>
+        <v>22.6412</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.32</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7655</v>
+        <v>0.749</v>
       </c>
       <c r="J135" t="n">
-        <v>17.6065</v>
+        <v>17.227</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>1.29</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7059</v>
+        <v>0.6861</v>
       </c>
       <c r="J136" t="n">
-        <v>16.2357</v>
+        <v>15.7803</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3374</v>
+        <v>0.3057</v>
       </c>
       <c r="J137" t="n">
-        <v>7.7602</v>
+        <v>7.0311</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>0.77</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2517</v>
+        <v>-0.2373</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.7891</v>
+        <v>-5.4579</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>0.73</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2901</v>
+        <v>-0.2763</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.6723</v>
+        <v>-6.3549</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.46</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5282</v>
+        <v>-0.53</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.1486</v>
+        <v>-12.19</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5698</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.949</v>
+        <v>-13.1054</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.42</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0061</v>
+        <v>1.0041</v>
       </c>
       <c r="J142" t="n">
-        <v>26.1586</v>
+        <v>26.1066</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.25</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6672</v>
+        <v>0.6327</v>
       </c>
       <c r="J143" t="n">
-        <v>17.3472</v>
+        <v>16.4502</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.05</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1841</v>
+        <v>0.1559</v>
       </c>
       <c r="J144" t="n">
-        <v>4.7866</v>
+        <v>4.0534</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.93</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2814</v>
+        <v>-0.2411</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.3164</v>
+        <v>-6.2686</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.92</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3098</v>
+        <v>-0.2685</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.0548</v>
+        <v>-6.981</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.41</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7723</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>20.0798</v>
+        <v>18.7278</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1272</v>
+        <v>0.096</v>
       </c>
       <c r="J148" t="n">
-        <v>3.3072</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0571</v>
+        <v>-0.045</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.4846</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1454</v>
+        <v>-0.126</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.7804</v>
+        <v>-3.276</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4445</v>
+        <v>-0.4388</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.557</v>
+        <v>-11.4088</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>0.98</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0217</v>
+        <v>-0.0144</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.5208</v>
+        <v>-0.3456</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0936</v>
+        <v>-0.0801</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.2464</v>
+        <v>-1.9224</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1301</v>
+        <v>-0.115</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.1224</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3648</v>
+        <v>-0.3506</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.7552</v>
+        <v>-8.414400000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4539</v>
+        <v>-0.4476</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.8936</v>
+        <v>-10.7424</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.53</v>
       </c>
       <c r="I157" t="n">
-        <v>1.132</v>
+        <v>1.1446</v>
       </c>
       <c r="J157" t="n">
-        <v>27.168</v>
+        <v>27.4704</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.41</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9533</v>
+        <v>0.9443</v>
       </c>
       <c r="J158" t="n">
-        <v>22.8792</v>
+        <v>22.6632</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5809</v>
+        <v>0.5507</v>
       </c>
       <c r="J159" t="n">
-        <v>13.9416</v>
+        <v>13.2168</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.1</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2998</v>
+        <v>0.2681</v>
       </c>
       <c r="J160" t="n">
-        <v>7.1952</v>
+        <v>6.4344</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>1.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="J161" t="n">
-        <v>4.5336</v>
+        <v>3.8688</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2169</v>
+        <v>1.2333</v>
       </c>
       <c r="J162" t="n">
-        <v>25.5549</v>
+        <v>25.8993</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.45</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0021</v>
+        <v>1.0049</v>
       </c>
       <c r="J163" t="n">
-        <v>21.0441</v>
+        <v>21.1029</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>20.0151</v>
+        <v>19.9311</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6698</v>
+        <v>0.6471</v>
       </c>
       <c r="J165" t="n">
-        <v>14.0658</v>
+        <v>13.5891</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.14</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3822</v>
+        <v>0.3504</v>
       </c>
       <c r="J166" t="n">
-        <v>8.026199999999999</v>
+        <v>7.3584</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.01</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1167</v>
+        <v>0.1016</v>
       </c>
       <c r="J167" t="n">
-        <v>2.4507</v>
+        <v>2.1336</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0041</v>
+        <v>0.0097</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.0861</v>
+        <v>0.2037</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.58</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4264</v>
+        <v>-0.4172</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.9544</v>
+        <v>-8.761200000000001</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.444</v>
+        <v>-0.4364</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.324</v>
+        <v>-9.164400000000001</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.48</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5142</v>
+        <v>-0.5144</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.7982</v>
+        <v>-10.8024</v>
       </c>
     </row>
   </sheetData>
